--- a/primary_vs_secondary_metals/scenario_data/metal_primary_secondary_shares.xlsx
+++ b/primary_vs_secondary_metals/scenario_data/metal_primary_secondary_shares.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shares" sheetId="1" r:id="Rd4191e4a78c34422"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" r:id="R0ea5548eaf904fe8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario assumptions" sheetId="3" r:id="R0299944e7ee345e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="4" r:id="Rd7614b98aaa1415b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shares" sheetId="1" r:id="Rb17ece4a654d4fb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" r:id="Rc87c421e38584852"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario assumptions" sheetId="3" r:id="Re09f96422c5d473e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="4" r:id="Rbb3db847087e4992"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -849,7 +849,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -925,11 +925,12 @@
     <x:xf numFmtId="203" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="2">
+  <x:dxfs count="4">
     <x:dxf>
       <x:fill>
         <x:patternFill>
@@ -944,13 +945,27 @@
         </x:patternFill>
       </x:fill>
     </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
   </x:dxfs>
 </x:styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MetalSharesTable" displayName="MetalSharesTable" ref="A4:J107">
-  <x:autoFilter ref="A4:J107"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MetalSharesTable" displayName="MetalSharesTable" ref="A4:J108" headerRowCount="1" totalsRowCount="0">
+  <x:autoFilter ref="A4:J108"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="YAML key"/>
     <x:tableColumn id="2" name="name"/>
@@ -4817,6 +4832,41 @@
         <x:v>OK</x:v>
       </x:c>
     </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="2" t="str">
+        <x:v>lithium carbonate</x:v>
+      </x:c>
+      <x:c r="B108" s="2" t="str">
+        <x:v>market for lithium carbonate</x:v>
+      </x:c>
+      <x:c r="C108" s="2" t="str">
+        <x:v>lithium carbonate</x:v>
+      </x:c>
+      <x:c r="D108" s="33" t="n">
+        <x:v>0.9991595853954618</x:v>
+      </x:c>
+      <x:c r="E108" s="33" t="n">
+        <x:v>0.9991595853954618</x:v>
+      </x:c>
+      <x:c r="F108" s="33" t="n">
+        <x:v>0.000840414604538239</x:v>
+      </x:c>
+      <x:c r="G108" s="33" t="n">
+        <x:v>0.000840414604538239</x:v>
+      </x:c>
+      <x:c r="H108" s="4" t="n">
+        <x:f>D108+F108</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I108" s="4" t="n">
+        <x:f>E108+G108</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J108" s="5" t="str">
+        <x:f>IF(AND(ROUND(H108,9)=1,ROUND(I108,9)=1),"OK","CHECK")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:J1"/>
@@ -4832,9 +4882,19 @@
       <x:formula>J5="CHECK"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="A108:J108">
+    <x:cfRule type="expression" dxfId="2" priority="5">
+      <x:formula>$J108="CHECK"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="J108:J108">
+    <x:cfRule type="expression" dxfId="3" priority="6">
+      <x:formula>J108="CHECK"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1f79ec4c0a94089"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad61bb8de7304403"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4917,10 +4977,10 @@
         <x:v>Updated scope</x:v>
       </x:c>
       <x:c r="B10" s="31" t="str">
-        <x:v>10 approved product rules</x:v>
+        <x:v>11 market rules / 10 metal families</x:v>
       </x:c>
       <x:c r="C10" s="31" t="str">
-        <x:v>2026-10-20</x:v>
+        <x:v>2026-10-22</x:v>
       </x:c>
       <x:c r="D10" s="31" t="str">
         <x:v>Native baseline and steel unchanged.</x:v>
@@ -4959,7 +5019,7 @@
         <x:v>Shares</x:v>
       </x:c>
       <x:c r="B13" s="31" t="str">
-        <x:v>103-product reference catalogue unchanged</x:v>
+        <x:v>104-product reference catalogue</x:v>
       </x:c>
       <x:c r="C13" s="31" t="str">
         <x:v>Optional input</x:v>
@@ -5012,7 +5072,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="15" t="str">
-        <x:v>Documentation snapshot, 20 October 2026. Runtime numbers come from the live YAML/CSV files; these sheets are not new model controls.</x:v>
+        <x:v>Documentation snapshot, 22 October 2026. Runtime numbers come from live YAML/CSV files; these sheets are not new model controls.</x:v>
       </x:c>
       <x:c r="B3" s="15"/>
       <x:c r="C3" s="15"/>
@@ -5271,6 +5331,27 @@
         <x:v>World / GLO</x:v>
       </x:c>
     </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="15" t="str">
+        <x:v>lithium carbonate</x:v>
+      </x:c>
+      <x:c r="B16" s="27" t="n">
+        <x:v>0.000840414604538239</x:v>
+      </x:c>
+      <x:c r="C16" s="25"/>
+      <x:c r="D16" s="25" t="n">
+        <x:v>0.22281639928698752</x:v>
+      </x:c>
+      <x:c r="E16" s="25" t="n">
+        <x:v>0.22281639928698752</x:v>
+      </x:c>
+      <x:c r="F16" s="25" t="n">
+        <x:v>0.37308461025982675</x:v>
+      </x:c>
+      <x:c r="G16" s="21" t="str">
+        <x:v>GLO</x:v>
+      </x:c>
+    </x:row>
     <x:row r="18">
       <x:c r="A18" s="18" t="str">
         <x:v>Case</x:v>
@@ -5338,10 +5419,10 @@
     </x:row>
     <x:row r="23" ht="40" customHeight="1">
       <x:c r="A23" s="15" t="str">
-        <x:v>Original six products</x:v>
+        <x:v>Non-precious products</x:v>
       </x:c>
       <x:c r="B23" s="31" t="str">
-        <x:v>Linear 2020-2050 floors; lithium uses global elemental-Li shares as a representative-compound/grade proxy.</x:v>
+        <x:v>Linear 2020-2050 floors. Both carbonate rules use global elemental-Li representative-compound sensitivities, not compound-grade forecasts.</x:v>
       </x:c>
       <x:c r="C23" s="31"/>
       <x:c r="D23" s="31"/>
@@ -5406,7 +5487,7 @@
         <x:v>Scope and deferred products</x:v>
       </x:c>
       <x:c r="B28" s="31" t="str">
-        <x:v>10 exact product rules. Zinc, tin, manganese, magnesium, rhodium and magnet materials remain native pending complete route/boundary review.</x:v>
+        <x:v>11 exact market rules / 10 metal families. Battery-grade GLO lithium and unsupported zinc, tin, manganese, magnesium, rhodium and magnet materials remain native.</x:v>
       </x:c>
       <x:c r="C28" s="31"/>
       <x:c r="D28" s="31"/>
@@ -5419,7 +5500,7 @@
         <x:v>Source of truth</x:v>
       </x:c>
       <x:c r="B29" s="31" t="str">
-        <x:v>Shares tab retains the 103-product reference catalogue. This is not 103 active overrides. Scenario assumptions/Evidence are documentation, not imported share controls.</x:v>
+        <x:v>Shares contains 104 reference products including ordinary carbonate, not 104 active overrides. YAML/CSV remain live controls; XLSX mode reads Shares only.</x:v>
       </x:c>
       <x:c r="C29" s="31"/>
       <x:c r="D29" s="31"/>
@@ -6027,6 +6108,21 @@
         <x:v>jm_pgm_2026</x:v>
       </x:c>
     </x:row>
+    <x:row r="38" ht="128" customHeight="1">
+      <x:c r="A38" s="31" t="str">
+        <x:v>lithium carbonate</x:v>
+      </x:c>
+      <x:c r="B38" s="31" t="str">
+        <x:v>GLO same-product hydrometallurgical recovery already supplies 0.08404146%. Rescale existing supplies, retaining recovery burdens, primary weights and logistics. IEA 2026 elemental-Li endpoints250/1122 and560/1501 are representative-compound sensitivities. Ordinary hydroxide benefits via its existing carbonate input (observed1.622797 kg/kg), without another floor or credit. Battery-grade GLO remains native. RELICS Lithium-only factors omit Spodumene; the indicator is not complete elemental-Li extraction.</x:v>
+      </x:c>
+      <x:c r="C38" s="31"/>
+      <x:c r="D38" s="31"/>
+      <x:c r="E38" s="31"/>
+      <x:c r="F38" s="31"/>
+      <x:c r="G38" s="31" t="str">
+        <x:v>iea_critical_minerals_2026, iea_recycling_2024; exported GLO inventory audit, 22 October 2026</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="B12:D12"/>
@@ -6066,6 +6162,7 @@
     <x:mergeCell ref="B35:F35"/>
     <x:mergeCell ref="B36:F36"/>
     <x:mergeCell ref="B37:F37"/>
+    <x:mergeCell ref="B38:F38"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/primary_vs_secondary_metals/scenario_data/metal_primary_secondary_shares.xlsx
+++ b/primary_vs_secondary_metals/scenario_data/metal_primary_secondary_shares.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shares" sheetId="1" r:id="Rb17ece4a654d4fb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" r:id="Rc87c421e38584852"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario assumptions" sheetId="3" r:id="Re09f96422c5d473e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="4" r:id="Rbb3db847087e4992"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shares" sheetId="1" r:id="R9d9b453302a1465c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" r:id="Re7deee483237404c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario assumptions" sheetId="3" r:id="Rce9498025a1249c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="4" r:id="R164536ebb8f64660"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,12 +13,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t xml:space="preserve">Metal primary/secondary shares map</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Edit the share columns (D:G). Columns H:J validate that primary + secondary = 1.0 for each year. YAML export included separately.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">YAML key</x:t>
   </x:si>
   <x:si>
@@ -685,13 +679,7 @@
     <x:t xml:space="preserve">Shares</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Main data table for metal shares</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Yes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Edit columns D:G if needed; H:J check row totals.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">README</x:t>
@@ -716,12 +704,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="5">
+  <x:numFmts count="7">
     <x:numFmt numFmtId="164" formatCode="0.###############"/>
     <x:numFmt numFmtId="200" formatCode="0.00%"/>
     <x:numFmt numFmtId="201" formatCode="0.000%"/>
     <x:numFmt numFmtId="202" formatCode="0.0000%"/>
     <x:numFmt numFmtId="203" formatCode="#,##0.0"/>
+    <x:numFmt numFmtId="204" formatCode="0.000000%"/>
+    <x:numFmt numFmtId="205" formatCode="0.000000"/>
   </x:numFmts>
   <x:fonts count="12">
     <x:font>
@@ -849,7 +839,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -926,6 +916,8 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="205" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -947,14 +939,14 @@
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -1167,8 +1159,8 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
-      <x:c r="A1" s="10" t="s">
-        <x:v>0</x:v>
+      <x:c r="A1" s="10" t="str">
+        <x:v>Primary/secondary model reference shares</x:v>
       </x:c>
       <x:c r="B1" s="11"/>
       <x:c r="C1" s="11"/>
@@ -1181,8 +1173,8 @@
       <x:c r="J1" s="11"/>
     </x:row>
     <x:row r="2" ht="32.04999923706055" customHeight="1">
-      <x:c r="A2" s="12" t="s">
-        <x:v>1</x:v>
+      <x:c r="A2" s="12" t="str">
+        <x:v>Reference fractions [0–1]: 2050 repeats the 2020 model reference, not a forecast. J checks four numeric inputs, bounds and paired totals. Future floors are on Scenario assumptions.</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
@@ -1197,3638 +1189,3638 @@
     <x:row r="3" ht="8.050000190734863" customHeight="1"/>
     <x:row r="4">
       <x:c r="A4" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B4" s="1" t="s">
+      <x:c r="D4" s="1" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
+      <x:c r="E4" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
+      <x:c r="F4" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E4" s="1" t="s">
+      <x:c r="G4" s="1" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F4" s="1" t="s">
+      <x:c r="H4" s="1" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G4" s="1" t="s">
+      <x:c r="I4" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H4" s="1" t="s">
+      <x:c r="J4" s="1" t="s">
         <x:v>9</x:v>
-      </x:c>
-      <x:c r="I4" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J4" s="1" t="s">
-        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D5" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E5" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F5" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H5" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D5" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F5" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G5" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H5" s="35" t="n">
         <x:f t="shared" ref="H5:H36" si="0">D5+F5</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I5" s="4" t="n">
+      <x:c r="I5" s="35" t="n">
         <x:f>E5+G5</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J5" s="5" t="str">
-        <x:f t="shared" ref="J5:J36" si="1">IF(AND(ROUND(H5,9)=1,ROUND(I5,9)=1),"OK","CHECK")</x:f>
+        <x:f t="shared" ref="J5:J36" si="1">IF(AND(ISNUMBER(D5),ISNUMBER(E5),ISNUMBER(F5),ISNUMBER(G5)),IF(AND(MIN(D5:G5)&gt;=0,MAX(D5:G5)&lt;=1,ABS(H5-1)&lt;=0.000001,ABS(I5-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E6" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F6" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H6" s="4">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D6" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F6" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H6" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I6" s="4" t="n">
+      <x:c r="I6" s="35" t="n">
         <x:f t="shared" ref="I6:I36" si="2">E6+G6</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J6" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D6),ISNUMBER(E6),ISNUMBER(F6),ISNUMBER(G6)),IF(AND(MIN(D6:G6)&gt;=0,MAX(D6:G6)&lt;=1,ABS(H6-1)&lt;=0.000001,ABS(I6-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D7" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E7" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F7" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H7" s="4">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D7" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F7" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G7" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I7" s="4">
+      <x:c r="I7" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J7" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D7),ISNUMBER(E7),ISNUMBER(F7),ISNUMBER(G7)),IF(AND(MIN(D7:G7)&gt;=0,MAX(D7:G7)&lt;=1,ABS(H7-1)&lt;=0.000001,ABS(I7-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D8" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E8" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F8" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H8" s="4">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D8" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F8" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I8" s="4">
+      <x:c r="I8" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J8" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D8),ISNUMBER(E8),ISNUMBER(F8),ISNUMBER(G8)),IF(AND(MIN(D8:G8)&gt;=0,MAX(D8:G8)&lt;=1,ABS(H8-1)&lt;=0.000001,ABS(I8-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D9" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E9" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F9" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H9" s="4">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D9" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F9" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H9" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I9" s="4">
+      <x:c r="I9" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J9" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D9),ISNUMBER(E9),ISNUMBER(F9),ISNUMBER(G9)),IF(AND(MIN(D9:G9)&gt;=0,MAX(D9:G9)&lt;=1,ABS(H9-1)&lt;=0.000001,ABS(I9-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D10" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E10" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F10" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H10" s="4">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D10" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E10" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F10" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H10" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I10" s="4">
+      <x:c r="I10" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J10" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D10),ISNUMBER(E10),ISNUMBER(F10),ISNUMBER(G10)),IF(AND(MIN(D10:G10)&gt;=0,MAX(D10:G10)&lt;=1,ABS(H10-1)&lt;=0.000001,ABS(I10-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D11" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E11" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F11" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H11" s="4">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D11" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E11" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F11" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H11" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I11" s="4">
+      <x:c r="I11" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D11),ISNUMBER(E11),ISNUMBER(F11),ISNUMBER(G11)),IF(AND(MIN(D11:G11)&gt;=0,MAX(D11:G11)&lt;=1,ABS(H11-1)&lt;=0.000001,ABS(I11-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D12" s="3">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D12" s="33">
         <x:v>0.311755</x:v>
       </x:c>
-      <x:c r="E12" s="3">
+      <x:c r="E12" s="33">
         <x:v>0.311755</x:v>
       </x:c>
-      <x:c r="F12" s="3">
+      <x:c r="F12" s="33">
         <x:v>0.688245</x:v>
       </x:c>
-      <x:c r="G12" s="3">
+      <x:c r="G12" s="33">
         <x:v>0.688245</x:v>
       </x:c>
-      <x:c r="H12" s="4">
+      <x:c r="H12" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I12" s="4">
+      <x:c r="I12" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D12),ISNUMBER(E12),ISNUMBER(F12),ISNUMBER(G12)),IF(AND(MIN(D12:G12)&gt;=0,MAX(D12:G12)&lt;=1,ABS(H12-1)&lt;=0.000001,ABS(I12-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B13" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D13" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E13" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F13" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H13" s="4">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D13" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E13" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F13" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I13" s="4">
+      <x:c r="I13" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J13" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D13),ISNUMBER(E13),ISNUMBER(F13),ISNUMBER(G13)),IF(AND(MIN(D13:G13)&gt;=0,MAX(D13:G13)&lt;=1,ABS(H13-1)&lt;=0.000001,ABS(I13-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C14" s="2" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D14" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E14" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F14" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H14" s="4">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D14" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E14" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F14" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G14" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H14" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I14" s="4">
+      <x:c r="I14" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D14),ISNUMBER(E14),ISNUMBER(F14),ISNUMBER(G14)),IF(AND(MIN(D14:G14)&gt;=0,MAX(D14:G14)&lt;=1,ABS(H14-1)&lt;=0.000001,ABS(I14-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D15" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E15" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F15" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H15" s="4">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D15" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E15" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F15" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I15" s="4">
+      <x:c r="I15" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D15),ISNUMBER(E15),ISNUMBER(F15),ISNUMBER(G15)),IF(AND(MIN(D15:G15)&gt;=0,MAX(D15:G15)&lt;=1,ABS(H15-1)&lt;=0.000001,ABS(I15-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C16" s="2" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D16" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E16" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F16" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H16" s="4">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D16" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E16" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F16" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I16" s="4">
+      <x:c r="I16" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J16" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D16),ISNUMBER(E16),ISNUMBER(F16),ISNUMBER(G16)),IF(AND(MIN(D16:G16)&gt;=0,MAX(D16:G16)&lt;=1,ABS(H16-1)&lt;=0.000001,ABS(I16-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C17" s="2" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D17" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E17" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F17" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H17" s="4">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D17" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E17" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F17" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I17" s="4">
+      <x:c r="I17" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J17" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D17),ISNUMBER(E17),ISNUMBER(F17),ISNUMBER(G17)),IF(AND(MIN(D17:G17)&gt;=0,MAX(D17:G17)&lt;=1,ABS(H17-1)&lt;=0.000001,ABS(I17-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B18" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C18" s="2" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D18" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E18" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F18" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H18" s="4">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D18" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E18" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F18" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G18" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H18" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I18" s="4">
+      <x:c r="I18" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J18" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D18),ISNUMBER(E18),ISNUMBER(F18),ISNUMBER(G18)),IF(AND(MIN(D18:G18)&gt;=0,MAX(D18:G18)&lt;=1,ABS(H18-1)&lt;=0.000001,ABS(I18-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B19" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C19" s="2" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D19" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E19" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F19" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H19" s="4">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D19" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E19" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F19" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G19" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I19" s="4">
+      <x:c r="I19" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J19" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D19),ISNUMBER(E19),ISNUMBER(F19),ISNUMBER(G19)),IF(AND(MIN(D19:G19)&gt;=0,MAX(D19:G19)&lt;=1,ABS(H19-1)&lt;=0.000001,ABS(I19-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B20" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C20" s="2" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D20" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E20" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F20" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H20" s="4">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D20" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E20" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F20" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G20" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H20" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I20" s="4">
+      <x:c r="I20" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J20" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D20),ISNUMBER(E20),ISNUMBER(F20),ISNUMBER(G20)),IF(AND(MIN(D20:G20)&gt;=0,MAX(D20:G20)&lt;=1,ABS(H20-1)&lt;=0.000001,ABS(I20-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B21" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C21" s="2" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D21" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E21" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F21" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H21" s="4">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D21" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E21" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F21" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G21" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H21" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I21" s="4">
+      <x:c r="I21" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J21" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D21),ISNUMBER(E21),ISNUMBER(F21),ISNUMBER(G21)),IF(AND(MIN(D21:G21)&gt;=0,MAX(D21:G21)&lt;=1,ABS(H21-1)&lt;=0.000001,ABS(I21-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C22" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D22" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E22" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F22" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H22" s="4">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D22" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E22" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F22" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G22" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H22" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I22" s="4">
+      <x:c r="I22" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J22" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D22),ISNUMBER(E22),ISNUMBER(F22),ISNUMBER(G22)),IF(AND(MIN(D22:G22)&gt;=0,MAX(D22:G22)&lt;=1,ABS(H22-1)&lt;=0.000001,ABS(I22-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B23" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C23" s="2" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D23" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E23" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F23" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H23" s="4">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D23" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E23" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F23" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G23" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H23" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I23" s="4">
+      <x:c r="I23" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J23" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D23),ISNUMBER(E23),ISNUMBER(F23),ISNUMBER(G23)),IF(AND(MIN(D23:G23)&gt;=0,MAX(D23:G23)&lt;=1,ABS(H23-1)&lt;=0.000001,ABS(I23-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B24" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C24" s="2" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D24" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E24" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F24" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H24" s="4">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D24" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E24" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F24" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G24" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H24" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I24" s="4">
+      <x:c r="I24" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J24" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D24),ISNUMBER(E24),ISNUMBER(F24),ISNUMBER(G24)),IF(AND(MIN(D24:G24)&gt;=0,MAX(D24:G24)&lt;=1,ABS(H24-1)&lt;=0.000001,ABS(I24-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B25" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C25" s="2" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D25" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E25" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F25" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H25" s="4">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D25" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E25" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F25" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G25" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H25" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I25" s="4">
+      <x:c r="I25" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J25" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D25),ISNUMBER(E25),ISNUMBER(F25),ISNUMBER(G25)),IF(AND(MIN(D25:G25)&gt;=0,MAX(D25:G25)&lt;=1,ABS(H25-1)&lt;=0.000001,ABS(I25-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B26" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C26" s="2" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D26" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E26" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F26" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H26" s="4">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D26" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E26" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F26" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G26" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H26" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I26" s="4">
+      <x:c r="I26" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J26" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D26),ISNUMBER(E26),ISNUMBER(F26),ISNUMBER(G26)),IF(AND(MIN(D26:G26)&gt;=0,MAX(D26:G26)&lt;=1,ABS(H26-1)&lt;=0.000001,ABS(I26-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B27" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C27" s="2" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D27" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E27" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F27" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G27" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H27" s="4">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D27" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E27" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F27" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G27" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H27" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I27" s="4">
+      <x:c r="I27" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J27" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D27),ISNUMBER(E27),ISNUMBER(F27),ISNUMBER(G27)),IF(AND(MIN(D27:G27)&gt;=0,MAX(D27:G27)&lt;=1,ABS(H27-1)&lt;=0.000001,ABS(I27-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="2" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C28" s="2" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D28" s="3">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D28" s="33">
         <x:v>0.99428374200000003</x:v>
       </x:c>
-      <x:c r="E28" s="3">
+      <x:c r="E28" s="33">
         <x:v>0.99428374200000003</x:v>
       </x:c>
-      <x:c r="F28" s="3">
+      <x:c r="F28" s="33">
         <x:v>5.7162580000000001E-3</x:v>
       </x:c>
-      <x:c r="G28" s="3">
+      <x:c r="G28" s="33">
         <x:v>5.7162580000000001E-3</x:v>
       </x:c>
-      <x:c r="H28" s="4">
+      <x:c r="H28" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I28" s="4">
+      <x:c r="I28" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J28" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D28),ISNUMBER(E28),ISNUMBER(F28),ISNUMBER(G28)),IF(AND(MIN(D28:G28)&gt;=0,MAX(D28:G28)&lt;=1,ABS(H28-1)&lt;=0.000001,ABS(I28-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B29" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C29" s="2" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D29" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E29" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F29" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G29" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H29" s="4">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D29" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E29" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F29" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G29" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H29" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I29" s="4">
+      <x:c r="I29" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J29" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D29),ISNUMBER(E29),ISNUMBER(F29),ISNUMBER(G29)),IF(AND(MIN(D29:G29)&gt;=0,MAX(D29:G29)&lt;=1,ABS(H29-1)&lt;=0.000001,ABS(I29-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B30" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C30" s="2" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D30" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E30" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F30" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G30" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H30" s="4">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D30" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E30" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F30" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G30" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H30" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I30" s="4">
+      <x:c r="I30" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J30" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D30),ISNUMBER(E30),ISNUMBER(F30),ISNUMBER(G30)),IF(AND(MIN(D30:G30)&gt;=0,MAX(D30:G30)&lt;=1,ABS(H30-1)&lt;=0.000001,ABS(I30-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B31" s="2" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C31" s="2" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D31" s="3">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D31" s="33">
         <x:v>0.8</x:v>
       </x:c>
-      <x:c r="E31" s="3">
+      <x:c r="E31" s="33">
         <x:v>0.8</x:v>
       </x:c>
-      <x:c r="F31" s="3">
+      <x:c r="F31" s="33">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="G31" s="3">
+      <x:c r="G31" s="33">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="H31" s="4">
+      <x:c r="H31" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I31" s="4">
+      <x:c r="I31" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J31" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D31),ISNUMBER(E31),ISNUMBER(F31),ISNUMBER(G31)),IF(AND(MIN(D31:G31)&gt;=0,MAX(D31:G31)&lt;=1,ABS(H31-1)&lt;=0.000001,ABS(I31-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B32" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C32" s="2" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D32" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E32" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F32" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G32" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H32" s="4">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D32" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E32" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F32" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G32" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H32" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I32" s="4">
+      <x:c r="I32" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J32" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D32),ISNUMBER(E32),ISNUMBER(F32),ISNUMBER(G32)),IF(AND(MIN(D32:G32)&gt;=0,MAX(D32:G32)&lt;=1,ABS(H32-1)&lt;=0.000001,ABS(I32-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B33" s="2" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C33" s="2" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D33" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E33" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F33" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G33" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H33" s="4">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D33" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E33" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F33" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G33" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H33" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I33" s="4">
+      <x:c r="I33" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J33" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D33),ISNUMBER(E33),ISNUMBER(F33),ISNUMBER(G33)),IF(AND(MIN(D33:G33)&gt;=0,MAX(D33:G33)&lt;=1,ABS(H33-1)&lt;=0.000001,ABS(I33-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B34" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C34" s="2" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D34" s="3">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D34" s="33">
         <x:v>0.995573343</x:v>
       </x:c>
-      <x:c r="E34" s="3">
+      <x:c r="E34" s="33">
         <x:v>0.995573343</x:v>
       </x:c>
-      <x:c r="F34" s="3">
+      <x:c r="F34" s="33">
         <x:v>4.4266569999999996E-3</x:v>
       </x:c>
-      <x:c r="G34" s="3">
+      <x:c r="G34" s="33">
         <x:v>4.4266569999999996E-3</x:v>
       </x:c>
-      <x:c r="H34" s="4">
+      <x:c r="H34" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I34" s="4">
+      <x:c r="I34" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J34" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D34),ISNUMBER(E34),ISNUMBER(F34),ISNUMBER(G34)),IF(AND(MIN(D34:G34)&gt;=0,MAX(D34:G34)&lt;=1,ABS(H34-1)&lt;=0.000001,ABS(I34-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B35" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C35" s="2" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D35" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E35" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F35" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G35" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H35" s="4">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D35" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E35" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F35" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G35" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H35" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I35" s="4">
+      <x:c r="I35" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J35" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D35),ISNUMBER(E35),ISNUMBER(F35),ISNUMBER(G35)),IF(AND(MIN(D35:G35)&gt;=0,MAX(D35:G35)&lt;=1,ABS(H35-1)&lt;=0.000001,ABS(I35-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B36" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C36" s="2" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D36" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E36" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F36" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G36" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H36" s="4">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D36" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E36" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F36" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G36" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H36" s="35">
         <x:f t="shared" si="0"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I36" s="4">
+      <x:c r="I36" s="35">
         <x:f t="shared" si="2"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J36" s="5" t="str">
-        <x:f t="shared" si="1"/>
+        <x:f t="shared" si="1">IF(AND(ISNUMBER(D36),ISNUMBER(E36),ISNUMBER(F36),ISNUMBER(G36)),IF(AND(MIN(D36:G36)&gt;=0,MAX(D36:G36)&lt;=1,ABS(H36-1)&lt;=0.000001,ABS(I36-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B37" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C37" s="2" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D37" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E37" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F37" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G37" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H37" s="4" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D37" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E37" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F37" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G37" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H37" s="35" t="n">
         <x:f t="shared" ref="H37:H68" si="3">D37+F37</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I37" s="4" t="n">
+      <x:c r="I37" s="35" t="n">
         <x:f t="shared" ref="I37:I68" si="4">E37+G37</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J37" s="5" t="str">
-        <x:f t="shared" ref="J37:J68" si="5">IF(AND(ROUND(H37,9)=1,ROUND(I37,9)=1),"OK","CHECK")</x:f>
+        <x:f t="shared" ref="J37:J68" si="5">IF(AND(ISNUMBER(D37),ISNUMBER(E37),ISNUMBER(F37),ISNUMBER(G37)),IF(AND(MIN(D37:G37)&gt;=0,MAX(D37:G37)&lt;=1,ABS(H37-1)&lt;=0.000001,ABS(I37-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B38" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C38" s="2" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D38" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E38" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F38" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G38" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H38" s="4">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D38" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E38" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F38" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G38" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H38" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I38" s="4">
+      <x:c r="I38" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J38" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D38),ISNUMBER(E38),ISNUMBER(F38),ISNUMBER(G38)),IF(AND(MIN(D38:G38)&gt;=0,MAX(D38:G38)&lt;=1,ABS(H38-1)&lt;=0.000001,ABS(I38-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B39" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C39" s="2" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D39" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E39" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F39" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G39" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H39" s="4">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D39" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E39" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F39" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G39" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H39" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I39" s="4">
+      <x:c r="I39" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J39" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D39),ISNUMBER(E39),ISNUMBER(F39),ISNUMBER(G39)),IF(AND(MIN(D39:G39)&gt;=0,MAX(D39:G39)&lt;=1,ABS(H39-1)&lt;=0.000001,ABS(I39-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B40" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C40" s="2" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D40" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E40" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F40" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G40" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H40" s="4">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D40" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E40" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F40" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G40" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H40" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I40" s="4">
+      <x:c r="I40" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J40" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D40),ISNUMBER(E40),ISNUMBER(F40),ISNUMBER(G40)),IF(AND(MIN(D40:G40)&gt;=0,MAX(D40:G40)&lt;=1,ABS(H40-1)&lt;=0.000001,ABS(I40-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="2" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B41" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C41" s="2" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D41" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E41" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F41" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G41" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H41" s="4">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D41" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E41" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F41" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G41" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H41" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I41" s="4">
+      <x:c r="I41" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J41" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D41),ISNUMBER(E41),ISNUMBER(F41),ISNUMBER(G41)),IF(AND(MIN(D41:G41)&gt;=0,MAX(D41:G41)&lt;=1,ABS(H41-1)&lt;=0.000001,ABS(I41-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B42" s="2" t="s">
-        <x:v>87</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C42" s="2" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D42" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E42" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F42" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G42" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H42" s="4">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D42" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E42" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F42" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G42" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H42" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I42" s="4">
+      <x:c r="I42" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J42" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D42),ISNUMBER(E42),ISNUMBER(F42),ISNUMBER(G42)),IF(AND(MIN(D42:G42)&gt;=0,MAX(D42:G42)&lt;=1,ABS(H42-1)&lt;=0.000001,ABS(I42-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="2" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B43" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C43" s="2" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D43" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E43" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F43" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G43" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H43" s="4">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D43" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E43" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F43" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G43" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H43" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I43" s="4">
+      <x:c r="I43" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J43" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D43),ISNUMBER(E43),ISNUMBER(F43),ISNUMBER(G43)),IF(AND(MIN(D43:G43)&gt;=0,MAX(D43:G43)&lt;=1,ABS(H43-1)&lt;=0.000001,ABS(I43-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="2" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B44" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C44" s="2" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D44" s="3">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D44" s="33">
         <x:v>0.45083796599999998</x:v>
       </x:c>
-      <x:c r="E44" s="3">
+      <x:c r="E44" s="33">
         <x:v>0.45083796599999998</x:v>
       </x:c>
-      <x:c r="F44" s="3">
+      <x:c r="F44" s="33">
         <x:v>0.54916203399999997</x:v>
       </x:c>
-      <x:c r="G44" s="3">
+      <x:c r="G44" s="33">
         <x:v>0.54916203399999997</x:v>
       </x:c>
-      <x:c r="H44" s="4">
+      <x:c r="H44" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I44" s="4">
+      <x:c r="I44" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J44" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D44),ISNUMBER(E44),ISNUMBER(F44),ISNUMBER(G44)),IF(AND(MIN(D44:G44)&gt;=0,MAX(D44:G44)&lt;=1,ABS(H44-1)&lt;=0.000001,ABS(I44-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="2" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B45" s="2" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C45" s="2" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D45" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E45" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F45" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G45" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H45" s="4">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D45" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E45" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F45" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G45" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H45" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I45" s="4">
+      <x:c r="I45" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J45" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D45),ISNUMBER(E45),ISNUMBER(F45),ISNUMBER(G45)),IF(AND(MIN(D45:G45)&gt;=0,MAX(D45:G45)&lt;=1,ABS(H45-1)&lt;=0.000001,ABS(I45-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="2" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B46" s="2" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C46" s="2" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D46" s="3">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D46" s="33">
         <x:v>0.99915958500000002</x:v>
       </x:c>
-      <x:c r="E46" s="3">
+      <x:c r="E46" s="33">
         <x:v>0.99915958500000002</x:v>
       </x:c>
-      <x:c r="F46" s="3">
+      <x:c r="F46" s="33">
         <x:v>8.4041460453823896E-4</x:v>
       </x:c>
-      <x:c r="G46" s="3">
+      <x:c r="G46" s="33">
         <x:v>8.4041460453823896E-4</x:v>
       </x:c>
-      <x:c r="H46" s="4">
+      <x:c r="H46" s="35">
         <x:f t="shared" si="3"/>
         <x:v>0.99999999960453823</x:v>
       </x:c>
-      <x:c r="I46" s="4">
+      <x:c r="I46" s="35">
         <x:f t="shared" si="4"/>
         <x:v>0.99999999960453823</x:v>
       </x:c>
       <x:c r="J46" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D46),ISNUMBER(E46),ISNUMBER(F46),ISNUMBER(G46)),IF(AND(MIN(D46:G46)&gt;=0,MAX(D46:G46)&lt;=1,ABS(H46-1)&lt;=0.000001,ABS(I46-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="2" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B47" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C47" s="2" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D47" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E47" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F47" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G47" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H47" s="4">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D47" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E47" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F47" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G47" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H47" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I47" s="4">
+      <x:c r="I47" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J47" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D47),ISNUMBER(E47),ISNUMBER(F47),ISNUMBER(G47)),IF(AND(MIN(D47:G47)&gt;=0,MAX(D47:G47)&lt;=1,ABS(H47-1)&lt;=0.000001,ABS(I47-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="2" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B48" s="2" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C48" s="2" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D48" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E48" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F48" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G48" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H48" s="4">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D48" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E48" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F48" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G48" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H48" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I48" s="4">
+      <x:c r="I48" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J48" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D48),ISNUMBER(E48),ISNUMBER(F48),ISNUMBER(G48)),IF(AND(MIN(D48:G48)&gt;=0,MAX(D48:G48)&lt;=1,ABS(H48-1)&lt;=0.000001,ABS(I48-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B49" s="2" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C49" s="2" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D49" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E49" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F49" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G49" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H49" s="4">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D49" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E49" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F49" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G49" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H49" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I49" s="4">
+      <x:c r="I49" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J49" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D49),ISNUMBER(E49),ISNUMBER(F49),ISNUMBER(G49)),IF(AND(MIN(D49:G49)&gt;=0,MAX(D49:G49)&lt;=1,ABS(H49-1)&lt;=0.000001,ABS(I49-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="2" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B50" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C50" s="2" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D50" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E50" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F50" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G50" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H50" s="4">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D50" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E50" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F50" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G50" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H50" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I50" s="4">
+      <x:c r="I50" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J50" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D50),ISNUMBER(E50),ISNUMBER(F50),ISNUMBER(G50)),IF(AND(MIN(D50:G50)&gt;=0,MAX(D50:G50)&lt;=1,ABS(H50-1)&lt;=0.000001,ABS(I50-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B51" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C51" s="2" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="D51" s="3">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D51" s="33">
         <x:v>0.99999751999999997</x:v>
       </x:c>
-      <x:c r="E51" s="3">
+      <x:c r="E51" s="33">
         <x:v>0.99999751999999997</x:v>
       </x:c>
-      <x:c r="F51" s="3">
+      <x:c r="F51" s="34">
         <x:v>2.48E-6</x:v>
       </x:c>
-      <x:c r="G51" s="3">
+      <x:c r="G51" s="34">
         <x:v>2.48E-6</x:v>
       </x:c>
-      <x:c r="H51" s="4">
+      <x:c r="H51" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I51" s="4">
+      <x:c r="I51" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J51" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D51),ISNUMBER(E51),ISNUMBER(F51),ISNUMBER(G51)),IF(AND(MIN(D51:G51)&gt;=0,MAX(D51:G51)&lt;=1,ABS(H51-1)&lt;=0.000001,ABS(I51-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B52" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C52" s="2" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D52" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E52" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F52" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G52" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H52" s="4">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D52" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E52" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F52" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G52" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H52" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I52" s="4">
+      <x:c r="I52" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J52" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D52),ISNUMBER(E52),ISNUMBER(F52),ISNUMBER(G52)),IF(AND(MIN(D52:G52)&gt;=0,MAX(D52:G52)&lt;=1,ABS(H52-1)&lt;=0.000001,ABS(I52-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="2" t="s">
-        <x:v>108</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B53" s="2" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C53" s="2" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="D53" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E53" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F53" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G53" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H53" s="4">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D53" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E53" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F53" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G53" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H53" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I53" s="4">
+      <x:c r="I53" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J53" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D53),ISNUMBER(E53),ISNUMBER(F53),ISNUMBER(G53)),IF(AND(MIN(D53:G53)&gt;=0,MAX(D53:G53)&lt;=1,ABS(H53-1)&lt;=0.000001,ABS(I53-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="2" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B54" s="2" t="s">
-        <x:v>111</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C54" s="2" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D54" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E54" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F54" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G54" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H54" s="4">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D54" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E54" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F54" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G54" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H54" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I54" s="4">
+      <x:c r="I54" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J54" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D54),ISNUMBER(E54),ISNUMBER(F54),ISNUMBER(G54)),IF(AND(MIN(D54:G54)&gt;=0,MAX(D54:G54)&lt;=1,ABS(H54-1)&lt;=0.000001,ABS(I54-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="2" t="s">
-        <x:v>112</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B55" s="2" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C55" s="2" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="D55" s="3">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D55" s="33">
         <x:v>0.99797153500000002</x:v>
       </x:c>
-      <x:c r="E55" s="3">
+      <x:c r="E55" s="33">
         <x:v>0.99797153500000002</x:v>
       </x:c>
-      <x:c r="F55" s="3">
+      <x:c r="F55" s="33">
         <x:v>2.0284650000000001E-3</x:v>
       </x:c>
-      <x:c r="G55" s="3">
+      <x:c r="G55" s="33">
         <x:v>2.0284650000000001E-3</x:v>
       </x:c>
-      <x:c r="H55" s="4">
+      <x:c r="H55" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I55" s="4">
+      <x:c r="I55" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J55" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D55),ISNUMBER(E55),ISNUMBER(F55),ISNUMBER(G55)),IF(AND(MIN(D55:G55)&gt;=0,MAX(D55:G55)&lt;=1,ABS(H55-1)&lt;=0.000001,ABS(I55-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B56" s="2" t="s">
-        <x:v>115</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C56" s="2" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D56" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E56" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F56" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G56" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H56" s="4">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D56" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E56" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F56" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G56" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H56" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I56" s="4">
+      <x:c r="I56" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J56" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D56),ISNUMBER(E56),ISNUMBER(F56),ISNUMBER(G56)),IF(AND(MIN(D56:G56)&gt;=0,MAX(D56:G56)&lt;=1,ABS(H56-1)&lt;=0.000001,ABS(I56-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="2" t="s">
-        <x:v>116</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B57" s="2" t="s">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C57" s="2" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="D57" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E57" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F57" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G57" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H57" s="4">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D57" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E57" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F57" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G57" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H57" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I57" s="4">
+      <x:c r="I57" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J57" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D57),ISNUMBER(E57),ISNUMBER(F57),ISNUMBER(G57)),IF(AND(MIN(D57:G57)&gt;=0,MAX(D57:G57)&lt;=1,ABS(H57-1)&lt;=0.000001,ABS(I57-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="2" t="s">
-        <x:v>118</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B58" s="2" t="s">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C58" s="2" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="D58" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E58" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F58" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G58" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H58" s="4">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D58" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E58" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F58" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G58" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H58" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I58" s="4">
+      <x:c r="I58" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J58" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D58),ISNUMBER(E58),ISNUMBER(F58),ISNUMBER(G58)),IF(AND(MIN(D58:G58)&gt;=0,MAX(D58:G58)&lt;=1,ABS(H58-1)&lt;=0.000001,ABS(I58-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="2" t="s">
-        <x:v>120</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B59" s="2" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C59" s="2" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D59" s="3">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D59" s="33">
         <x:v>0.84451447599999996</x:v>
       </x:c>
-      <x:c r="E59" s="3">
+      <x:c r="E59" s="33">
         <x:v>0.84451447599999996</x:v>
       </x:c>
-      <x:c r="F59" s="3">
+      <x:c r="F59" s="33">
         <x:v>0.15548552400000001</x:v>
       </x:c>
-      <x:c r="G59" s="3">
+      <x:c r="G59" s="33">
         <x:v>0.15548552400000001</x:v>
       </x:c>
-      <x:c r="H59" s="4">
+      <x:c r="H59" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I59" s="4">
+      <x:c r="I59" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J59" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D59),ISNUMBER(E59),ISNUMBER(F59),ISNUMBER(G59)),IF(AND(MIN(D59:G59)&gt;=0,MAX(D59:G59)&lt;=1,ABS(H59-1)&lt;=0.000001,ABS(I59-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="2" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B60" s="2" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C60" s="2" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D60" s="3">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D60" s="33">
         <x:v>0.95539961399999995</x:v>
       </x:c>
-      <x:c r="E60" s="3">
+      <x:c r="E60" s="33">
         <x:v>0.95539961399999995</x:v>
       </x:c>
-      <x:c r="F60" s="3">
+      <x:c r="F60" s="33">
         <x:v>4.4600385999999999E-2</x:v>
       </x:c>
-      <x:c r="G60" s="3">
+      <x:c r="G60" s="33">
         <x:v>4.4600385999999999E-2</x:v>
       </x:c>
-      <x:c r="H60" s="4">
+      <x:c r="H60" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I60" s="4">
+      <x:c r="I60" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J60" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D60),ISNUMBER(E60),ISNUMBER(F60),ISNUMBER(G60)),IF(AND(MIN(D60:G60)&gt;=0,MAX(D60:G60)&lt;=1,ABS(H60-1)&lt;=0.000001,ABS(I60-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="2" t="s">
-        <x:v>124</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B61" s="2" t="s">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C61" s="2" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="D61" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E61" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F61" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G61" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H61" s="4">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D61" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E61" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F61" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G61" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H61" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I61" s="4">
+      <x:c r="I61" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J61" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D61),ISNUMBER(E61),ISNUMBER(F61),ISNUMBER(G61)),IF(AND(MIN(D61:G61)&gt;=0,MAX(D61:G61)&lt;=1,ABS(H61-1)&lt;=0.000001,ABS(I61-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="2" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B62" s="2" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C62" s="2" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="D62" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E62" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F62" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G62" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H62" s="4">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D62" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E62" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F62" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G62" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H62" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I62" s="4">
+      <x:c r="I62" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J62" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D62),ISNUMBER(E62),ISNUMBER(F62),ISNUMBER(G62)),IF(AND(MIN(D62:G62)&gt;=0,MAX(D62:G62)&lt;=1,ABS(H62-1)&lt;=0.000001,ABS(I62-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="2" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B63" s="2" t="s">
-        <x:v>129</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C63" s="2" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D63" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E63" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F63" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G63" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H63" s="4">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D63" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E63" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F63" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G63" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H63" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I63" s="4">
+      <x:c r="I63" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J63" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D63),ISNUMBER(E63),ISNUMBER(F63),ISNUMBER(G63)),IF(AND(MIN(D63:G63)&gt;=0,MAX(D63:G63)&lt;=1,ABS(H63-1)&lt;=0.000001,ABS(I63-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="2" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B64" s="2" t="s">
-        <x:v>131</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C64" s="2" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D64" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E64" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F64" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G64" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H64" s="4">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D64" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E64" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F64" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G64" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H64" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I64" s="4">
+      <x:c r="I64" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J64" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D64),ISNUMBER(E64),ISNUMBER(F64),ISNUMBER(G64)),IF(AND(MIN(D64:G64)&gt;=0,MAX(D64:G64)&lt;=1,ABS(H64-1)&lt;=0.000001,ABS(I64-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="2" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B65" s="2" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C65" s="2" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="D65" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E65" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F65" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G65" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H65" s="4">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D65" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E65" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F65" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G65" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H65" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I65" s="4">
+      <x:c r="I65" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J65" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D65),ISNUMBER(E65),ISNUMBER(F65),ISNUMBER(G65)),IF(AND(MIN(D65:G65)&gt;=0,MAX(D65:G65)&lt;=1,ABS(H65-1)&lt;=0.000001,ABS(I65-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B66" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C66" s="2" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D66" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E66" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F66" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G66" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H66" s="4">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D66" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E66" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F66" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G66" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H66" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I66" s="4">
+      <x:c r="I66" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J66" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D66),ISNUMBER(E66),ISNUMBER(F66),ISNUMBER(G66)),IF(AND(MIN(D66:G66)&gt;=0,MAX(D66:G66)&lt;=1,ABS(H66-1)&lt;=0.000001,ABS(I66-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="2" t="s">
-        <x:v>136</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B67" s="2" t="s">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C67" s="2" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="D67" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E67" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F67" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G67" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H67" s="4">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D67" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E67" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F67" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G67" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H67" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I67" s="4">
+      <x:c r="I67" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J67" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D67),ISNUMBER(E67),ISNUMBER(F67),ISNUMBER(G67)),IF(AND(MIN(D67:G67)&gt;=0,MAX(D67:G67)&lt;=1,ABS(H67-1)&lt;=0.000001,ABS(I67-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="2" t="s">
-        <x:v>138</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B68" s="2" t="s">
-        <x:v>139</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C68" s="2" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="D68" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E68" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F68" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G68" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H68" s="4">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D68" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E68" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F68" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G68" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H68" s="35">
         <x:f t="shared" si="3"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I68" s="4">
+      <x:c r="I68" s="35">
         <x:f t="shared" si="4"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J68" s="5" t="str">
-        <x:f t="shared" si="5"/>
+        <x:f t="shared" si="5">IF(AND(ISNUMBER(D68),ISNUMBER(E68),ISNUMBER(F68),ISNUMBER(G68)),IF(AND(MIN(D68:G68)&gt;=0,MAX(D68:G68)&lt;=1,ABS(H68-1)&lt;=0.000001,ABS(I68-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="2" t="s">
-        <x:v>140</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B69" s="2" t="s">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C69" s="2" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D69" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E69" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F69" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G69" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H69" s="4" t="n">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="D69" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E69" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F69" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G69" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H69" s="35" t="n">
         <x:f t="shared" ref="H69:H100" si="6">D69+F69</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I69" s="4" t="n">
+      <x:c r="I69" s="35" t="n">
         <x:f t="shared" ref="I69:I100" si="7">E69+G69</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J69" s="5" t="str">
-        <x:f t="shared" ref="J69:J100" si="8">IF(AND(ROUND(H69,9)=1,ROUND(I69,9)=1),"OK","CHECK")</x:f>
+        <x:f t="shared" ref="J69:J100" si="8">IF(AND(ISNUMBER(D69),ISNUMBER(E69),ISNUMBER(F69),ISNUMBER(G69)),IF(AND(MIN(D69:G69)&gt;=0,MAX(D69:G69)&lt;=1,ABS(H69-1)&lt;=0.000001,ABS(I69-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="2" t="s">
-        <x:v>142</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B70" s="2" t="s">
-        <x:v>143</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C70" s="2" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="D70" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E70" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F70" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G70" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H70" s="4">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D70" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E70" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F70" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G70" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H70" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I70" s="4">
+      <x:c r="I70" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J70" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D70),ISNUMBER(E70),ISNUMBER(F70),ISNUMBER(G70)),IF(AND(MIN(D70:G70)&gt;=0,MAX(D70:G70)&lt;=1,ABS(H70-1)&lt;=0.000001,ABS(I70-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="2" t="s">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B71" s="2" t="s">
-        <x:v>145</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C71" s="2" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="D71" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E71" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F71" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G71" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H71" s="4">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D71" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E71" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F71" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G71" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H71" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I71" s="4">
+      <x:c r="I71" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J71" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D71),ISNUMBER(E71),ISNUMBER(F71),ISNUMBER(G71)),IF(AND(MIN(D71:G71)&gt;=0,MAX(D71:G71)&lt;=1,ABS(H71-1)&lt;=0.000001,ABS(I71-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="2" t="s">
-        <x:v>146</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B72" s="2" t="s">
-        <x:v>147</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C72" s="2" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="D72" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E72" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F72" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G72" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H72" s="4">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D72" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E72" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F72" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G72" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H72" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I72" s="4">
+      <x:c r="I72" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J72" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D72),ISNUMBER(E72),ISNUMBER(F72),ISNUMBER(G72)),IF(AND(MIN(D72:G72)&gt;=0,MAX(D72:G72)&lt;=1,ABS(H72-1)&lt;=0.000001,ABS(I72-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="2" t="s">
-        <x:v>148</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B73" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C73" s="2" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="D73" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E73" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F73" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G73" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H73" s="4">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D73" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E73" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F73" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G73" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H73" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I73" s="4">
+      <x:c r="I73" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J73" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D73),ISNUMBER(E73),ISNUMBER(F73),ISNUMBER(G73)),IF(AND(MIN(D73:G73)&gt;=0,MAX(D73:G73)&lt;=1,ABS(H73-1)&lt;=0.000001,ABS(I73-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B74" s="2" t="s">
-        <x:v>151</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C74" s="2" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="D74" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E74" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F74" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G74" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H74" s="4">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D74" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E74" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F74" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G74" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H74" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I74" s="4">
+      <x:c r="I74" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J74" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D74),ISNUMBER(E74),ISNUMBER(F74),ISNUMBER(G74)),IF(AND(MIN(D74:G74)&gt;=0,MAX(D74:G74)&lt;=1,ABS(H74-1)&lt;=0.000001,ABS(I74-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="2" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B75" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C75" s="2" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="D75" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E75" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F75" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G75" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H75" s="4">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D75" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E75" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F75" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G75" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H75" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I75" s="4">
+      <x:c r="I75" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J75" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D75),ISNUMBER(E75),ISNUMBER(F75),ISNUMBER(G75)),IF(AND(MIN(D75:G75)&gt;=0,MAX(D75:G75)&lt;=1,ABS(H75-1)&lt;=0.000001,ABS(I75-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="2" t="s">
-        <x:v>154</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B76" s="2" t="s">
-        <x:v>155</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C76" s="2" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="D76" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E76" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F76" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G76" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H76" s="4">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D76" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E76" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F76" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G76" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H76" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I76" s="4">
+      <x:c r="I76" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J76" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D76),ISNUMBER(E76),ISNUMBER(F76),ISNUMBER(G76)),IF(AND(MIN(D76:G76)&gt;=0,MAX(D76:G76)&lt;=1,ABS(H76-1)&lt;=0.000001,ABS(I76-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="2" t="s">
-        <x:v>156</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B77" s="2" t="s">
-        <x:v>157</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C77" s="2" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="D77" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E77" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F77" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G77" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H77" s="4">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D77" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E77" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F77" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G77" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H77" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I77" s="4">
+      <x:c r="I77" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J77" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D77),ISNUMBER(E77),ISNUMBER(F77),ISNUMBER(G77)),IF(AND(MIN(D77:G77)&gt;=0,MAX(D77:G77)&lt;=1,ABS(H77-1)&lt;=0.000001,ABS(I77-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="2" t="s">
-        <x:v>158</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B78" s="2" t="s">
-        <x:v>159</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C78" s="2" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="D78" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E78" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F78" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G78" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H78" s="4">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D78" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E78" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F78" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G78" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H78" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I78" s="4">
+      <x:c r="I78" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J78" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D78),ISNUMBER(E78),ISNUMBER(F78),ISNUMBER(G78)),IF(AND(MIN(D78:G78)&gt;=0,MAX(D78:G78)&lt;=1,ABS(H78-1)&lt;=0.000001,ABS(I78-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="2" t="s">
-        <x:v>160</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B79" s="2" t="s">
-        <x:v>161</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C79" s="2" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="D79" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E79" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F79" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G79" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H79" s="4">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D79" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E79" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F79" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G79" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H79" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I79" s="4">
+      <x:c r="I79" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J79" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D79),ISNUMBER(E79),ISNUMBER(F79),ISNUMBER(G79)),IF(AND(MIN(D79:G79)&gt;=0,MAX(D79:G79)&lt;=1,ABS(H79-1)&lt;=0.000001,ABS(I79-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="2" t="s">
-        <x:v>162</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B80" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C80" s="2" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="D80" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E80" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F80" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G80" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H80" s="4">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D80" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E80" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F80" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G80" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H80" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I80" s="4">
+      <x:c r="I80" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J80" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D80),ISNUMBER(E80),ISNUMBER(F80),ISNUMBER(G80)),IF(AND(MIN(D80:G80)&gt;=0,MAX(D80:G80)&lt;=1,ABS(H80-1)&lt;=0.000001,ABS(I80-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="2" t="s">
-        <x:v>164</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B81" s="2" t="s">
-        <x:v>165</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C81" s="2" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="D81" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E81" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F81" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G81" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H81" s="4">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="D81" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E81" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F81" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G81" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H81" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I81" s="4">
+      <x:c r="I81" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J81" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D81),ISNUMBER(E81),ISNUMBER(F81),ISNUMBER(G81)),IF(AND(MIN(D81:G81)&gt;=0,MAX(D81:G81)&lt;=1,ABS(H81-1)&lt;=0.000001,ABS(I81-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="2" t="s">
-        <x:v>166</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B82" s="2" t="s">
-        <x:v>167</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C82" s="2" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="D82" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E82" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F82" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G82" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H82" s="4">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D82" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E82" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F82" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G82" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H82" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I82" s="4">
+      <x:c r="I82" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J82" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D82),ISNUMBER(E82),ISNUMBER(F82),ISNUMBER(G82)),IF(AND(MIN(D82:G82)&gt;=0,MAX(D82:G82)&lt;=1,ABS(H82-1)&lt;=0.000001,ABS(I82-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="2" t="s">
-        <x:v>168</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B83" s="2" t="s">
-        <x:v>169</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C83" s="2" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="D83" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E83" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F83" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G83" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H83" s="4">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="D83" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E83" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F83" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G83" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H83" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I83" s="4">
+      <x:c r="I83" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J83" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D83),ISNUMBER(E83),ISNUMBER(F83),ISNUMBER(G83)),IF(AND(MIN(D83:G83)&gt;=0,MAX(D83:G83)&lt;=1,ABS(H83-1)&lt;=0.000001,ABS(I83-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="2" t="s">
-        <x:v>170</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B84" s="2" t="s">
-        <x:v>171</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C84" s="2" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="D84" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E84" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F84" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G84" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H84" s="4">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D84" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E84" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F84" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G84" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H84" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I84" s="4">
+      <x:c r="I84" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J84" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D84),ISNUMBER(E84),ISNUMBER(F84),ISNUMBER(G84)),IF(AND(MIN(D84:G84)&gt;=0,MAX(D84:G84)&lt;=1,ABS(H84-1)&lt;=0.000001,ABS(I84-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="2" t="s">
-        <x:v>172</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B85" s="2" t="s">
-        <x:v>173</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C85" s="2" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="D85" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E85" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F85" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G85" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H85" s="4">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D85" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E85" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F85" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G85" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H85" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I85" s="4">
+      <x:c r="I85" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J85" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D85),ISNUMBER(E85),ISNUMBER(F85),ISNUMBER(G85)),IF(AND(MIN(D85:G85)&gt;=0,MAX(D85:G85)&lt;=1,ABS(H85-1)&lt;=0.000001,ABS(I85-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="2" t="s">
-        <x:v>174</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B86" s="2" t="s">
-        <x:v>175</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C86" s="2" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="D86" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E86" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F86" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G86" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H86" s="4">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="D86" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E86" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F86" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G86" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H86" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I86" s="4">
+      <x:c r="I86" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J86" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D86),ISNUMBER(E86),ISNUMBER(F86),ISNUMBER(G86)),IF(AND(MIN(D86:G86)&gt;=0,MAX(D86:G86)&lt;=1,ABS(H86-1)&lt;=0.000001,ABS(I86-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="2" t="s">
-        <x:v>176</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B87" s="2" t="s">
-        <x:v>177</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C87" s="2" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="D87" s="3">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="D87" s="33">
         <x:v>0.91536347699999998</x:v>
       </x:c>
-      <x:c r="E87" s="3">
+      <x:c r="E87" s="33">
         <x:v>0.91536347699999998</x:v>
       </x:c>
-      <x:c r="F87" s="3">
+      <x:c r="F87" s="33">
         <x:v>8.4636523000000005E-2</x:v>
       </x:c>
-      <x:c r="G87" s="3">
+      <x:c r="G87" s="33">
         <x:v>8.4636523000000005E-2</x:v>
       </x:c>
-      <x:c r="H87" s="4">
+      <x:c r="H87" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I87" s="4">
+      <x:c r="I87" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J87" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D87),ISNUMBER(E87),ISNUMBER(F87),ISNUMBER(G87)),IF(AND(MIN(D87:G87)&gt;=0,MAX(D87:G87)&lt;=1,ABS(H87-1)&lt;=0.000001,ABS(I87-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="2" t="s">
-        <x:v>178</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B88" s="2" t="s">
-        <x:v>179</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C88" s="2" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="D88" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E88" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F88" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G88" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H88" s="4">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D88" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E88" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F88" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G88" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H88" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I88" s="4">
+      <x:c r="I88" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J88" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D88),ISNUMBER(E88),ISNUMBER(F88),ISNUMBER(G88)),IF(AND(MIN(D88:G88)&gt;=0,MAX(D88:G88)&lt;=1,ABS(H88-1)&lt;=0.000001,ABS(I88-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="2" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B89" s="2" t="s">
-        <x:v>181</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C89" s="2" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="D89" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E89" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F89" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G89" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H89" s="4">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D89" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E89" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F89" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G89" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H89" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I89" s="4">
+      <x:c r="I89" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J89" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D89),ISNUMBER(E89),ISNUMBER(F89),ISNUMBER(G89)),IF(AND(MIN(D89:G89)&gt;=0,MAX(D89:G89)&lt;=1,ABS(H89-1)&lt;=0.000001,ABS(I89-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="2" t="s">
-        <x:v>182</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B90" s="2" t="s">
-        <x:v>183</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C90" s="2" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="D90" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E90" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F90" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G90" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H90" s="4">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D90" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E90" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F90" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G90" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H90" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I90" s="4">
+      <x:c r="I90" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J90" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D90),ISNUMBER(E90),ISNUMBER(F90),ISNUMBER(G90)),IF(AND(MIN(D90:G90)&gt;=0,MAX(D90:G90)&lt;=1,ABS(H90-1)&lt;=0.000001,ABS(I90-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="2" t="s">
-        <x:v>184</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B91" s="2" t="s">
-        <x:v>185</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C91" s="2" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="D91" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E91" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F91" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G91" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H91" s="4">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D91" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E91" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F91" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G91" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H91" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I91" s="4">
+      <x:c r="I91" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J91" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D91),ISNUMBER(E91),ISNUMBER(F91),ISNUMBER(G91)),IF(AND(MIN(D91:G91)&gt;=0,MAX(D91:G91)&lt;=1,ABS(H91-1)&lt;=0.000001,ABS(I91-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="2" t="s">
-        <x:v>186</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B92" s="2" t="s">
-        <x:v>187</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C92" s="2" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="D92" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E92" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F92" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G92" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H92" s="4">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="D92" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E92" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F92" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G92" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H92" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I92" s="4">
+      <x:c r="I92" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J92" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D92),ISNUMBER(E92),ISNUMBER(F92),ISNUMBER(G92)),IF(AND(MIN(D92:G92)&gt;=0,MAX(D92:G92)&lt;=1,ABS(H92-1)&lt;=0.000001,ABS(I92-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="2" t="s">
-        <x:v>188</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B93" s="2" t="s">
-        <x:v>189</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C93" s="2" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="D93" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E93" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F93" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G93" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H93" s="4">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D93" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E93" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F93" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G93" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H93" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I93" s="4">
+      <x:c r="I93" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J93" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D93),ISNUMBER(E93),ISNUMBER(F93),ISNUMBER(G93)),IF(AND(MIN(D93:G93)&gt;=0,MAX(D93:G93)&lt;=1,ABS(H93-1)&lt;=0.000001,ABS(I93-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="2" t="s">
-        <x:v>190</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B94" s="2" t="s">
-        <x:v>191</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C94" s="2" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="D94" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E94" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F94" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G94" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H94" s="4">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="D94" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E94" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F94" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G94" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H94" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I94" s="4">
+      <x:c r="I94" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J94" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D94),ISNUMBER(E94),ISNUMBER(F94),ISNUMBER(G94)),IF(AND(MIN(D94:G94)&gt;=0,MAX(D94:G94)&lt;=1,ABS(H94-1)&lt;=0.000001,ABS(I94-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="2" t="s">
-        <x:v>192</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B95" s="2" t="s">
-        <x:v>193</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C95" s="2" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="D95" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E95" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F95" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G95" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H95" s="4">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="D95" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E95" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F95" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G95" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H95" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I95" s="4">
+      <x:c r="I95" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J95" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D95),ISNUMBER(E95),ISNUMBER(F95),ISNUMBER(G95)),IF(AND(MIN(D95:G95)&gt;=0,MAX(D95:G95)&lt;=1,ABS(H95-1)&lt;=0.000001,ABS(I95-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="2" t="s">
-        <x:v>194</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B96" s="2" t="s">
-        <x:v>195</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C96" s="2" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="D96" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E96" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F96" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G96" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H96" s="4">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D96" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E96" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F96" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G96" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H96" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I96" s="4">
+      <x:c r="I96" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J96" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D96),ISNUMBER(E96),ISNUMBER(F96),ISNUMBER(G96)),IF(AND(MIN(D96:G96)&gt;=0,MAX(D96:G96)&lt;=1,ABS(H96-1)&lt;=0.000001,ABS(I96-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="2" t="s">
-        <x:v>196</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B97" s="2" t="s">
-        <x:v>197</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C97" s="2" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="D97" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E97" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F97" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G97" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H97" s="4">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D97" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E97" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F97" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G97" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H97" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I97" s="4">
+      <x:c r="I97" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J97" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D97),ISNUMBER(E97),ISNUMBER(F97),ISNUMBER(G97)),IF(AND(MIN(D97:G97)&gt;=0,MAX(D97:G97)&lt;=1,ABS(H97-1)&lt;=0.000001,ABS(I97-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="2" t="s">
-        <x:v>198</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B98" s="2" t="s">
-        <x:v>199</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C98" s="2" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="D98" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E98" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F98" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G98" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H98" s="4">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="D98" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E98" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F98" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G98" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H98" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I98" s="4">
+      <x:c r="I98" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J98" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D98),ISNUMBER(E98),ISNUMBER(F98),ISNUMBER(G98)),IF(AND(MIN(D98:G98)&gt;=0,MAX(D98:G98)&lt;=1,ABS(H98-1)&lt;=0.000001,ABS(I98-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="2" t="s">
-        <x:v>200</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B99" s="2" t="s">
-        <x:v>201</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C99" s="2" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="D99" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E99" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F99" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G99" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H99" s="4">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D99" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E99" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F99" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G99" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H99" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I99" s="4">
+      <x:c r="I99" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J99" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D99),ISNUMBER(E99),ISNUMBER(F99),ISNUMBER(G99)),IF(AND(MIN(D99:G99)&gt;=0,MAX(D99:G99)&lt;=1,ABS(H99-1)&lt;=0.000001,ABS(I99-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="2" t="s">
-        <x:v>202</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B100" s="2" t="s">
-        <x:v>203</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C100" s="2" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D100" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E100" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F100" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G100" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H100" s="4">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D100" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E100" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F100" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G100" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H100" s="35">
         <x:f t="shared" si="6"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I100" s="4">
+      <x:c r="I100" s="35">
         <x:f t="shared" si="7"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J100" s="5" t="str">
-        <x:f t="shared" si="8"/>
+        <x:f t="shared" si="8">IF(AND(ISNUMBER(D100),ISNUMBER(E100),ISNUMBER(F100),ISNUMBER(G100)),IF(AND(MIN(D100:G100)&gt;=0,MAX(D100:G100)&lt;=1,ABS(H100-1)&lt;=0.000001,ABS(I100-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="2" t="s">
-        <x:v>204</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B101" s="2" t="s">
-        <x:v>205</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C101" s="2" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="D101" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E101" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F101" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G101" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H101" s="4" t="n">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D101" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E101" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F101" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G101" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H101" s="35" t="n">
         <x:f t="shared" ref="H101:H107" si="9">D101+F101</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I101" s="4" t="n">
+      <x:c r="I101" s="35" t="n">
         <x:f t="shared" ref="I101:I107" si="10">E101+G101</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J101" s="5" t="str">
-        <x:f t="shared" ref="J101:J107" si="11">IF(AND(ROUND(H101,9)=1,ROUND(I101,9)=1),"OK","CHECK")</x:f>
+        <x:f t="shared" ref="J101:J107" si="11">IF(AND(ISNUMBER(D101),ISNUMBER(E101),ISNUMBER(F101),ISNUMBER(G101)),IF(AND(MIN(D101:G101)&gt;=0,MAX(D101:G101)&lt;=1,ABS(H101-1)&lt;=0.000001,ABS(I101-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="2" t="s">
-        <x:v>206</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B102" s="2" t="s">
-        <x:v>207</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C102" s="2" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="D102" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E102" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F102" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G102" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H102" s="4">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="D102" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E102" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F102" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G102" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H102" s="35">
         <x:f t="shared" si="9"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I102" s="4">
+      <x:c r="I102" s="35">
         <x:f t="shared" si="10"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J102" s="5" t="str">
-        <x:f t="shared" si="11"/>
+        <x:f t="shared" si="11">IF(AND(ISNUMBER(D102),ISNUMBER(E102),ISNUMBER(F102),ISNUMBER(G102)),IF(AND(MIN(D102:G102)&gt;=0,MAX(D102:G102)&lt;=1,ABS(H102-1)&lt;=0.000001,ABS(I102-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="2" t="s">
-        <x:v>208</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B103" s="2" t="s">
-        <x:v>209</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C103" s="2" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="D103" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E103" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F103" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G103" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H103" s="4">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D103" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E103" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F103" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G103" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H103" s="35">
         <x:f t="shared" si="9"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I103" s="4">
+      <x:c r="I103" s="35">
         <x:f t="shared" si="10"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J103" s="5" t="str">
-        <x:f t="shared" si="11"/>
+        <x:f t="shared" si="11">IF(AND(ISNUMBER(D103),ISNUMBER(E103),ISNUMBER(F103),ISNUMBER(G103)),IF(AND(MIN(D103:G103)&gt;=0,MAX(D103:G103)&lt;=1,ABS(H103-1)&lt;=0.000001,ABS(I103-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="2" t="s">
-        <x:v>210</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B104" s="2" t="s">
-        <x:v>211</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C104" s="2" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="D104" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E104" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F104" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G104" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H104" s="4">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="D104" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E104" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F104" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G104" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H104" s="35">
         <x:f t="shared" si="9"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I104" s="4">
+      <x:c r="I104" s="35">
         <x:f t="shared" si="10"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J104" s="5" t="str">
-        <x:f t="shared" si="11"/>
+        <x:f t="shared" si="11">IF(AND(ISNUMBER(D104),ISNUMBER(E104),ISNUMBER(F104),ISNUMBER(G104)),IF(AND(MIN(D104:G104)&gt;=0,MAX(D104:G104)&lt;=1,ABS(H104-1)&lt;=0.000001,ABS(I104-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="2" t="s">
-        <x:v>212</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B105" s="2" t="s">
-        <x:v>213</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C105" s="2" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="D105" s="3">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D105" s="33">
         <x:v>0.99993377999999999</x:v>
       </x:c>
-      <x:c r="E105" s="3">
+      <x:c r="E105" s="33">
         <x:v>0.99993377999999999</x:v>
       </x:c>
-      <x:c r="F105" s="3">
+      <x:c r="F105" s="33">
         <x:v>6.622E-5</x:v>
       </x:c>
-      <x:c r="G105" s="3">
+      <x:c r="G105" s="33">
         <x:v>6.622E-5</x:v>
       </x:c>
-      <x:c r="H105" s="4">
+      <x:c r="H105" s="35">
         <x:f t="shared" si="9"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I105" s="4">
+      <x:c r="I105" s="35">
         <x:f t="shared" si="10"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J105" s="5" t="str">
-        <x:f t="shared" si="11"/>
+        <x:f t="shared" si="11">IF(AND(ISNUMBER(D105),ISNUMBER(E105),ISNUMBER(F105),ISNUMBER(G105)),IF(AND(MIN(D105:G105)&gt;=0,MAX(D105:G105)&lt;=1,ABS(H105-1)&lt;=0.000001,ABS(I105-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="2" t="s">
-        <x:v>214</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B106" s="2" t="s">
-        <x:v>215</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C106" s="2" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="D106" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E106" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F106" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G106" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H106" s="4">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D106" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E106" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F106" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G106" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H106" s="35">
         <x:f t="shared" si="9"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I106" s="4">
+      <x:c r="I106" s="35">
         <x:f t="shared" si="10"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J106" s="5" t="str">
-        <x:f t="shared" si="11"/>
+        <x:f t="shared" si="11">IF(AND(ISNUMBER(D106),ISNUMBER(E106),ISNUMBER(F106),ISNUMBER(G106)),IF(AND(MIN(D106:G106)&gt;=0,MAX(D106:G106)&lt;=1,ABS(H106-1)&lt;=0.000001,ABS(I106-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="2" t="s">
-        <x:v>216</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B107" s="2" t="s">
-        <x:v>217</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C107" s="2" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="D107" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E107" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F107" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G107" s="3">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H107" s="4">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D107" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E107" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F107" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G107" s="33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H107" s="35">
         <x:f t="shared" si="9"/>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I107" s="4">
+      <x:c r="I107" s="35">
         <x:f t="shared" si="10"/>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J107" s="5" t="str">
-        <x:f t="shared" si="11"/>
+        <x:f t="shared" si="11">IF(AND(ISNUMBER(D107),ISNUMBER(E107),ISNUMBER(F107),ISNUMBER(G107)),IF(AND(MIN(D107:G107)&gt;=0,MAX(D107:G107)&lt;=1,ABS(H107-1)&lt;=0.000001,ABS(I107-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
@@ -4854,16 +4846,16 @@
       <x:c r="G108" s="33" t="n">
         <x:v>0.000840414604538239</x:v>
       </x:c>
-      <x:c r="H108" s="4" t="n">
+      <x:c r="H108" s="35" t="n">
         <x:f>D108+F108</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I108" s="4" t="n">
+      <x:c r="I108" s="35" t="n">
         <x:f>E108+G108</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J108" s="5" t="str">
-        <x:f>IF(AND(ROUND(H108,9)=1,ROUND(I108,9)=1),"OK","CHECK")</x:f>
+        <x:f>IF(AND(ISNUMBER(D108),ISNUMBER(E108),ISNUMBER(F108),ISNUMBER(G108)),IF(AND(MIN(D108:G108)&gt;=0,MAX(D108:G108)&lt;=1,ABS(H108-1)&lt;=0.000001,ABS(I108-1)&lt;=0.000001),"OK","CHECK"),"CHECK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
@@ -4894,7 +4886,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad61bb8de7304403"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72c629bdf2744d05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4911,7 +4903,7 @@
   <x:sheetData>
     <x:row r="1" ht="18.299999237060547">
       <x:c r="A1" s="13" t="s">
-        <x:v>218</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B1" s="11"/>
       <x:c r="C1" s="11"/>
@@ -4919,54 +4911,54 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="6" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="C3" s="6" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="B3" s="6" t="s">
+      <x:c r="D3" s="6" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="C3" s="6" t="s">
+    </x:row>
+    <x:row r="4" ht="70" customHeight="1">
+      <x:c r="A4" s="7" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="D3" s="6" t="s">
+      <x:c r="B4" s="7" t="str">
+        <x:v>Model reference shares, not global observations</x:v>
+      </x:c>
+      <x:c r="C4" s="8" t="s">
         <x:v>222</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="7" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="B4" s="7" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="D4" s="7" t="s">
-        <x:v>226</x:v>
+      <x:c r="D4" s="7" t="str">
+        <x:v>D:G are fractions from 0 to 1, displayed as percentages. J rejects missing, text, out-of-range or non-normalized inputs (tolerance 0.000001).</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="7" t="s">
-        <x:v>227</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
-        <x:v>228</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C5" s="8" t="s">
-        <x:v>229</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>230</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="9" t="s">
-        <x:v>231</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="14" t="s">
-        <x:v>232</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B8" s="11"/>
       <x:c r="C8" s="11"/>
@@ -5026,6 +5018,62 @@
       </x:c>
       <x:c r="D13" s="31" t="str">
         <x:v>Only the Shares sheet is read when METALS_SHARE_SOURCE = xlsx.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="72" customHeight="1">
+      <x:c r="A14" s="31" t="str">
+        <x:v>Reference source</x:v>
+      </x:c>
+      <x:c r="B14" s="31" t="str">
+        <x:v>103 pinned premise records + generic carbonate</x:v>
+      </x:c>
+      <x:c r="C14" s="31" t="str">
+        <x:v>Model inputs</x:v>
+      </x:c>
+      <x:c r="D14" s="31" t="str">
+        <x:v>Original catalogue commit d5362d8ce1df66c20c7e71c91051a1b88e46c583. Generic carbonate is the separately reviewed GLO market reference.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="72" customHeight="1">
+      <x:c r="A15" s="31" t="str">
+        <x:v>2050 reference columns</x:v>
+      </x:c>
+      <x:c r="B15" s="31" t="str">
+        <x:v>Held equal to 2020 in this workbook</x:v>
+      </x:c>
+      <x:c r="C15" s="31" t="str">
+        <x:v>Not forecasts</x:v>
+      </x:c>
+      <x:c r="D15" s="31" t="str">
+        <x:v>Future conservative/moderate/high floors are separate scenario assumptions. Do not replace these reference fractions with observed 2025 recycling rates.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="72" customHeight="1">
+      <x:c r="A16" s="31" t="str">
+        <x:v>Zero secondary</x:v>
+      </x:c>
+      <x:c r="B16" s="31" t="str">
+        <x:v>No secondary share in this model reference</x:v>
+      </x:c>
+      <x:c r="C16" s="31" t="str">
+        <x:v>Not a global zero</x:v>
+      </x:c>
+      <x:c r="D16" s="31" t="str">
+        <x:v>A zero does not establish that recycling is physically impossible or absent worldwide. Only 11 market rules are approved; presence and grade must match.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="90" customHeight="1">
+      <x:c r="A17" s="31" t="str">
+        <x:v>Evidence integration, 23 October 2026</x:v>
+      </x:c>
+      <x:c r="B17" s="31" t="str">
+        <x:v>Revised CSV connected to scenario files and reports</x:v>
+      </x:c>
+      <x:c r="C17" s="31" t="str">
+        <x:v>2020 references unchanged</x:v>
+      </x:c>
+      <x:c r="D17" s="31" t="str">
+        <x:v>2050 scenario floors and source qualifications updated. Default YAML/CSV generation is separate from the held-reference Shares table. Native baseline and endogenous steel are unchanged. Rebuild notebook 1 and recalculate notebook 2 to update results.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5072,7 +5120,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="15" t="str">
-        <x:v>Documentation snapshot, 22 October 2026. Runtime numbers come from live YAML/CSV files; these sheets are not new model controls.</x:v>
+        <x:v>Documentation snapshot, 23 October 2026. Runtime numbers come from live YAML/CSV files; these sheets are not new model controls.</x:v>
       </x:c>
       <x:c r="B3" s="15"/>
       <x:c r="C3" s="15"/>
@@ -5090,24 +5138,27 @@
       <x:c r="F4" s="15"/>
       <x:c r="G4" s="15"/>
     </x:row>
-    <x:row r="5" ht="32" customHeight="1">
+    <x:row r="5" ht="44" customHeight="1">
       <x:c r="A5" s="20" t="str">
         <x:v>Product</x:v>
       </x:c>
       <x:c r="B5" s="20" t="str">
-        <x:v>2020 reference</x:v>
+        <x:v>2020 model reference</x:v>
       </x:c>
       <x:c r="C5" s="20" t="str">
-        <x:v>2025 supply anchor</x:v>
+        <x:v>2025 physical-supply anchor</x:v>
       </x:c>
       <x:c r="D5" s="20" t="str">
-        <x:v>2050 conservative</x:v>
+        <x:v>conservative
+2050 floor</x:v>
       </x:c>
       <x:c r="E5" s="20" t="str">
-        <x:v>2050 moderate</x:v>
+        <x:v>moderate_recycling
+2050 floor</x:v>
       </x:c>
       <x:c r="F5" s="20" t="str">
-        <x:v>2050 high</x:v>
+        <x:v>high_recycling
+2050 floor</x:v>
       </x:c>
       <x:c r="G5" s="20" t="str">
         <x:v>Market scope</x:v>
@@ -5125,10 +5176,10 @@
         <x:v>0.45</x:v>
       </x:c>
       <x:c r="E6" s="25" t="n">
-        <x:v>0.6</x:v>
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="F6" s="25" t="n">
-        <x:v>0.7</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="G6" s="21" t="str">
         <x:v>World / GLO</x:v>
@@ -5164,10 +5215,10 @@
       </x:c>
       <x:c r="C8" s="25"/>
       <x:c r="D8" s="25" t="n">
-        <x:v>0.2</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="E8" s="25" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="F8" s="25" t="n">
         <x:v>0.3</x:v>
@@ -5227,7 +5278,7 @@
       </x:c>
       <x:c r="C11" s="25"/>
       <x:c r="D11" s="25" t="n">
-        <x:v>0.22281639928698752</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="E11" s="25" t="n">
         <x:v>0.22281639928698752</x:v>
@@ -5247,6 +5298,7 @@
         <x:v>0.004426657</x:v>
       </x:c>
       <x:c r="C12" s="25" t="n">
+        <x:f>Evidence!F6</x:f>
         <x:v>0.27666029669615244</x:v>
       </x:c>
       <x:c r="D12" s="25" t="n">
@@ -5270,6 +5322,7 @@
         <x:v>0.084636523</x:v>
       </x:c>
       <x:c r="C13" s="25" t="n">
+        <x:f>Evidence!F7</x:f>
         <x:v>0.18923577858647767</x:v>
       </x:c>
       <x:c r="D13" s="25" t="n">
@@ -5293,6 +5346,7 @@
         <x:v>0.044600386</x:v>
       </x:c>
       <x:c r="C14" s="25" t="n">
+        <x:f>Evidence!F8</x:f>
         <x:v>0.21776463963963963</x:v>
       </x:c>
       <x:c r="D14" s="25" t="n">
@@ -5316,6 +5370,7 @@
         <x:v>0.155485524</x:v>
       </x:c>
       <x:c r="C15" s="25" t="n">
+        <x:f>Evidence!F9</x:f>
         <x:v>0.3223981900452489</x:v>
       </x:c>
       <x:c r="D15" s="25" t="n">
@@ -5340,13 +5395,13 @@
       </x:c>
       <x:c r="C16" s="25"/>
       <x:c r="D16" s="25" t="n">
-        <x:v>0.22281639928698752</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="E16" s="25" t="n">
         <x:v>0.22281639928698752</x:v>
       </x:c>
       <x:c r="F16" s="25" t="n">
-        <x:v>0.37308461025982675</x:v>
+        <x:v>0.3730846102598268</x:v>
       </x:c>
       <x:c r="G16" s="21" t="str">
         <x:v>GLO</x:v>
@@ -5393,10 +5448,10 @@
     </x:row>
     <x:row r="21" ht="40" customHeight="1">
       <x:c r="A21" s="15" t="str">
-        <x:v>conservative / moderate / high</x:v>
+        <x:v>Minimum cases</x:v>
       </x:c>
       <x:c r="B21" s="31" t="str">
-        <x:v>Minimum floors: applied secondary = max(native share, interpolated floor). Primary/non-secondary remainder = 1 - secondary.</x:v>
+        <x:v>conservative / moderate_recycling / high_recycling: applied secondary = max(native share, interpolated floor); primary/non-secondary remainder = 1 - secondary. These are 2050 floors, not fixed shares at every year or site.</x:v>
       </x:c>
       <x:c r="C21" s="31"/>
       <x:c r="D21" s="31"/>
@@ -5443,12 +5498,12 @@
       <x:c r="F24" s="31"/>
       <x:c r="G24" s="31"/>
     </x:row>
-    <x:row r="25" ht="40" customHeight="1">
+    <x:row r="25" ht="78" customHeight="1">
       <x:c r="A25" s="15" t="str">
         <x:v>Future increments</x:v>
       </x:c>
       <x:c r="B25" s="31" t="str">
-        <x:v>Analyst sensitivity assumptions, not published 2050 forecasts. Endpoints clamp outside the stated interval. No scrap-stock feasibility is solved.</x:v>
+        <x:v>Al/Cu floors are analyst sensitivities. Ni/Co use rounded IEA battery-derived secondary supply / global total demand, not grade-specific forecasts. Li 15% is analyst-selected; 22.3/37.3% are derived source ratios. Pb 77% is literature-based; its brackets and precious-metal increments are sensitivities.</x:v>
       </x:c>
       <x:c r="C25" s="31"/>
       <x:c r="D25" s="31"/>
@@ -5482,12 +5537,12 @@
       <x:c r="F27" s="31"/>
       <x:c r="G27" s="31"/>
     </x:row>
-    <x:row r="28" ht="40" customHeight="1">
+    <x:row r="28" ht="66" customHeight="1">
       <x:c r="A28" s="15" t="str">
         <x:v>Scope and deferred products</x:v>
       </x:c>
       <x:c r="B28" s="31" t="str">
-        <x:v>11 exact market rules / 10 metal families. Battery-grade GLO lithium and unsupported zinc, tin, manganese, magnesium, rhodium and magnet materials remain native.</x:v>
+        <x:v>11 exact market rules / 10 metal families remain approved. Revised candidate figures do not enable zinc, graphite, tin, other unsupported metals or any rare-earth market. Thirteen non-magnet REE products retain reference curves in the generated files.</x:v>
       </x:c>
       <x:c r="C28" s="31"/>
       <x:c r="D28" s="31"/>
@@ -5500,7 +5555,7 @@
         <x:v>Source of truth</x:v>
       </x:c>
       <x:c r="B29" s="31" t="str">
-        <x:v>Shares contains 104 reference products including ordinary carbonate, not 104 active overrides. YAML/CSV remain live controls; XLSX mode reads Shares only.</x:v>
+        <x:v>Shares contains 104 model reference products, not 104 active overrides or measured global recycling rates. YAML/CSV are live defaults; XLSX mode reads only Shares A:G. Other sheets document assumptions.</x:v>
       </x:c>
       <x:c r="C29" s="31"/>
       <x:c r="D29" s="31"/>
@@ -5520,6 +5575,19 @@
       <x:c r="E30" s="31"/>
       <x:c r="F30" s="31"/>
       <x:c r="G30" s="31"/>
+    </x:row>
+    <x:row r="31" ht="65" customHeight="1">
+      <x:c r="A31" s="15" t="str">
+        <x:v>Scope versus coverage</x:v>
+      </x:c>
+      <x:c r="B31" s="31" t="str">
+        <x:v>Market scope lists eligible locations, not proof that a market is present. In the inspected 3.12 exports the World battery-grade carbonate rule is absent; battery-grade GLO remains native. Read actual native/target/applied shares in each export audit.</x:v>
+      </x:c>
+      <x:c r="C31" s="31"/>
+      <x:c r="D31" s="31"/>
+      <x:c r="E31" s="31"/>
+      <x:c r="F31" s="31"/>
+      <x:c r="G31" s="31"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5535,6 +5603,7 @@
     <x:mergeCell ref="B28:G28"/>
     <x:mergeCell ref="B29:G29"/>
     <x:mergeCell ref="B30:G30"/>
+    <x:mergeCell ref="B31:G31"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5745,7 +5814,7 @@
       <x:c r="F12" s="18"/>
       <x:c r="G12" s="18"/>
     </x:row>
-    <x:row r="13" ht="110" customHeight="1">
+    <x:row r="13" ht="134" customHeight="1">
       <x:c r="A13" s="31" t="str">
         <x:v>iea_recycling_2024</x:v>
       </x:c>
@@ -5755,7 +5824,7 @@
       <x:c r="C13" s="31"/>
       <x:c r="D13" s="31"/>
       <x:c r="E13" s="31" t="str">
-        <x:v>Accessed 2026-10-13. Supports higher secondary supply and the need to distinguish recycled input from collection and recovery rates. Battery-metal and whole-metal markets are not interchangeable; configured nickel/cobalt targets are screening assumptions, not direct reproductions of an IEA scenario.</x:v>
+        <x:v>IEA 2024 Fig. 2.16 (p68): 2050 battery-derived secondary Ni / global total Ni demand is roughly 15%, just over 20%, 30%; Co roughly 20%, almost 30%, 40% in STEPS/APS/NZE. Repo Ni 22% is a rounded proxy, not an exact reported point. Battery scrap + retired EV/storage recovery excludes other secondary sources.</x:v>
       </x:c>
       <x:c r="F13" s="31"/>
       <x:c r="G13" s="31"/>
@@ -5770,12 +5839,12 @@
       <x:c r="C14" s="31"/>
       <x:c r="D14" s="31"/>
       <x:c r="E14" s="31" t="str">
-        <x:v>Accessed 2026-10-13. Reports an EU 2050 end-of-life scrap contribution to refined copper of approximately 26-29%. It does not establish a global cathode target.</x:v>
+        <x:v>Rechecked 2026-10-22. ICA Europe 2050: 0.9–1.0 Mt end-of-life scrap / 3.4 Mt refined EU copper = 26.47–29.41%. The repo 25/35/45% global cathode floors are analyst sensitivities, not that EU forecast.</x:v>
       </x:c>
       <x:c r="F14" s="31"/>
       <x:c r="G14" s="31"/>
     </x:row>
-    <x:row r="15" ht="110" customHeight="1">
+    <x:row r="15" ht="126" customHeight="1">
       <x:c r="A15" s="31" t="str">
         <x:v>jrc_aluminium_2024</x:v>
       </x:c>
@@ -5785,7 +5854,7 @@
       <x:c r="C15" s="31"/>
       <x:c r="D15" s="31"/>
       <x:c r="E15" s="31" t="str">
-        <x:v>Accessed 2026-10-13. Supports secondary production as a decarbonisation route; not a source for an exact global cast-alloy 70% recycled-content forecast.</x:v>
+        <x:v>JRC (printed p34/PDF p36): 60 Mt BAU and &gt;70 Mt maximised-collection post-consumer recycling in 2050 are volumes, not percentages. Revised 45/55/65% global cast-alloy floors are analyst sensitivities. The 68.8245% model reference already exceeds all three; a higher native share is retained.</x:v>
       </x:c>
       <x:c r="F15" s="31"/>
       <x:c r="G15" s="31"/>
@@ -5800,12 +5869,12 @@
       <x:c r="C16" s="31"/>
       <x:c r="D16" s="31"/>
       <x:c r="E16" s="31" t="str">
-        <x:v>Accessed 2026-10-13. Stock-flow-informed scenarios include 77% secondary lead in 2050. The 65% and 85% endpoints below bracket this as repo sensitivities.</x:v>
+        <x:v>Rechecked 2026-10-22. Van der Voet et al. (online 2018; journal issue 2019), p5: 77% secondary lead production in 2050. This extrapolates historical recycling trends. Repo 65% and 85% are analyst brackets, not additional reported forecasts.</x:v>
       </x:c>
       <x:c r="F16" s="31"/>
       <x:c r="G16" s="31"/>
     </x:row>
-    <x:row r="17" ht="110" customHeight="1">
+    <x:row r="17" ht="140" customHeight="1">
       <x:c r="A17" s="31" t="str">
         <x:v>iea_critical_minerals_2026</x:v>
       </x:c>
@@ -5815,7 +5884,7 @@
       <x:c r="C17" s="31"/>
       <x:c r="D17" s="31"/>
       <x:c r="E17" s="31" t="str">
-        <x:v>Accessed 2026-10-20. Pages 145 and 350 give approximate 2050 recycled lithium supply of 250 kt in the STEPS-context base case and 560 kt in HDS, against total global demand of 1122 and 1501 kt Li respectively. Derived fractions are about 22.3% and 37.3%, not measured battery-grade carbonate shares. No complete 2026 intermediate-year recycling series was verified.</x:v>
+        <x:v>Source quantities independently rechecked 2026-10-23: IEA 2026 pp145/350 gives about 250/1122 kt Li in STEPS context and 560/1501 kt in HDS, or 22.3/37.3%. Conservative 15% is an analyst lower-collection sensitivity. Rounded numerators, elemental-Li-to-compound transfer and the linear ramp limit interpretation; these are not grade-specific forecasts.</x:v>
       </x:c>
       <x:c r="F17" s="31"/>
       <x:c r="G17" s="31"/>
@@ -5830,7 +5899,7 @@
       <x:c r="C18" s="31"/>
       <x:c r="D18" s="31"/>
       <x:c r="E18" s="31" t="str">
-        <x:v>Accessed 2026-10-20; published 2026-01-29. 2025 physical supply anchor: recycled 1404.3 t divided by mine 3671.6 t plus recycled 1404.3 t = 0.2766602966961524. Excludes net producer hedging. This is not a 2050 forecast. Hold this anchor in conservative; add 0.10 and 0.20 absolute share in moderate/high as analyst-selected sensitivities.</x:v>
+        <x:v>Rechecked WGC full-year 2025 supply on 2026-10-22: mine 3671.6 t + recycled 1404.3 t gives 27.6660%. These are reported supply estimates, not measured content of the LCI market. Net producer hedging is excluded. Conservative holds the anchor; moderate/high add 10/20 percentage points as analyst sensitivities.</x:v>
       </x:c>
       <x:c r="F18" s="31"/>
       <x:c r="G18" s="31"/>
@@ -5845,7 +5914,7 @@
       <x:c r="C19" s="31"/>
       <x:c r="D19" s="31"/>
       <x:c r="E19" s="31" t="str">
-        <x:v>Accessed 2026-10-20. 2025 physical supply anchor: recycled 197.6 Moz divided by mine 846.6 Moz plus recycled 197.6 Moz = 0.1892357785864777. Excludes hedging, official sector sales and stock movements. The 2050 increments are analyst sensitivities, not published projections.</x:v>
+        <x:v>Rechecked against the Silver Institute 15 April 2026 release: mine 846.6 + recycled 197.6 Moz gives 18.9236%. Denominator excludes net hedging, net official-sector sales and stock adjustments. Reported supply estimate, not LCI-market content; future 10/20-point increments are analyst sensitivities.</x:v>
       </x:c>
       <x:c r="F19" s="31"/>
       <x:c r="G19" s="31"/>
@@ -5860,7 +5929,7 @@
       <x:c r="C20" s="31"/>
       <x:c r="D20" s="31"/>
       <x:c r="E20" s="31" t="str">
-        <x:v>Accessed 2026-10-20; published 2026-05-14. May 2026 report pp27-30, 2025 actual estimates in thousand troy oz: Pt secondary1547/(primary5557+secondary1547)=0.2177646396396396; Pd secondary3135/(primary6589+secondary3135)=0.3223981900452489. Open-loop secondary supply; industrial demand is net of closed-loop recycling. No extra industrial closed-loop contribution is added. These are 2025 anchors; 2050 increments are analyst-selected sensitivities.</x:v>
+        <x:v>Rechecked Johnson Matthey May 2026 pp27/29: 2025 Pt primary5557 + secondary1547 gives 21.7765%; Pd6589 +3135 gives 32.2398% (thousand troy oz). Secondary is open-loop recovery; industrial demand is net of closed-loop recycling. Reported estimates, not LCI-market content or 2050 forecasts.</x:v>
       </x:c>
       <x:c r="F20" s="31"/>
       <x:c r="G20" s="31"/>
@@ -5890,7 +5959,7 @@
       <x:c r="C22" s="31"/>
       <x:c r="D22" s="31"/>
       <x:c r="E22" s="31" t="str">
-        <x:v>Not implemented: mixed-feed precious-metal recycling LCI (Au/Ag/Pt/Pd/Rh). Public inventory at https://doi.org/10.6092/unibo/amsacta/8288. Allocation, collection boundaries and global representativeness require review before import.</x:v>
+        <x:v>Not implemented. Cespi et al. 2025 integrated Northern Italian refinery LCI: Au/Ag/Pt/Pd/Rh, not global share projections. Dataset https://doi.org/10.6092/unibo/amsacta/8288 is CC BY-NC 4.0; review licence, allocation, collection boundaries and representativeness before reuse.</x:v>
       </x:c>
       <x:c r="F22" s="31"/>
       <x:c r="G22" s="31"/>
@@ -5920,7 +5989,7 @@
       <x:c r="C24" s="31"/>
       <x:c r="D24" s="31"/>
       <x:c r="E24" s="31" t="str">
-        <x:v>Not implemented: global refined-tin RIR sensitivities40-60%, not validated forecasts. A complete secondary-tin recovery/purification LCI and collection boundaries must be connected before activation.</x:v>
+        <x:v>Not implemented. Chowdhury et al. 2026, section3.6: 40–60% refined-tin recycled-input rates are sensitivities, not forecasts or end-of-life recycling rates. Overall RIR includes manufacturing scrap. A complete compatible recovery/purification LCI and collection boundary are still required.</x:v>
       </x:c>
       <x:c r="F24" s="31"/>
       <x:c r="G24" s="31"/>
@@ -5958,12 +6027,12 @@
         <x:v>Source IDs</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="100" customHeight="1">
+    <x:row r="28" ht="116" customHeight="1">
       <x:c r="A28" s="31" t="str">
         <x:v>aluminium, cast alloy</x:v>
       </x:c>
       <x:c r="B28" s="31" t="str">
-        <x:v>Curves come from the selected scenario file. Minimum mode retains a higher native share instead of imposing the 45%/60% source endpoints. Future fractions are sensitivities, not validated cast-alloy forecasts.</x:v>
+        <x:v>Revised floors 45/55/65% are low-confidence analyst sensitivities, not JRC global cast-alloy projections. JRC quantities are Mt, not percentages. Because the reference is 68.8245%, minimum mode can retain the native share unchanged in all cases. Existing grade and recycling burdens remain.</x:v>
       </x:c>
       <x:c r="C28" s="31"/>
       <x:c r="D28" s="31"/>
@@ -5988,12 +6057,12 @@
         <x:v>ica_copper_2023, iea_recycling_2024</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="100" customHeight="1">
+    <x:row r="30" ht="116" customHeight="1">
       <x:c r="A30" s="31" t="str">
         <x:v>nickel, class 1</x:v>
       </x:c>
       <x:c r="B30" s="31" t="str">
-        <x:v>Existing same-grade recycling providers only. These scenarios scale the existing electronics-scrap recovery recipe; they do not invent a future battery-grade nickel process, or assign whole-sector recycled nickel percentages directly to nickel class 1 without qualification.</x:v>
+        <x:v>15/22/30% are rounded battery-derived secondary nickel / global total nickel demand proxies (IEA 2024 Fig. 2.16), excluding stainless-steel recycling. Applying them to the existing class-1 electronics-scrap recovery recipe is an explicit low-confidence technology/grade sensitivity, not a class-1 forecast.</x:v>
       </x:c>
       <x:c r="C30" s="31"/>
       <x:c r="D30" s="31"/>
@@ -6003,12 +6072,12 @@
         <x:v>iea_recycling_2024</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="100" customHeight="1">
+    <x:row r="31" ht="116" customHeight="1">
       <x:c r="A31" s="31" t="str">
         <x:v>cobalt</x:v>
       </x:c>
       <x:c r="B31" s="31" t="str">
-        <x:v>Scales the existing hydrometallurgical/pyrometallurgical recovery recipe. The 40% case is deliberately exploratory and is not directly inferred from the IEA percentage reduction in new mine development.</x:v>
+        <x:v>20/30/40% are rounded IEA battery-derived secondary cobalt / global total cobalt demand proxies, including manufacturing scrap and retired EV/storage batteries. Other secondary sources are excluded. Existing hydro/pyrometallurgical recovery burdens remain; product-grade content and collection capacity are not solved.</x:v>
       </x:c>
       <x:c r="C31" s="31"/>
       <x:c r="D31" s="31"/>
@@ -6023,7 +6092,7 @@
         <x:v>lead</x:v>
       </x:c>
       <x:c r="B32" s="31" t="str">
-        <x:v>Lower/upper sensitivity around the literature 77% secondary-production figure. The same remelting/recovery burdens are retained, not credited away.</x:v>
+        <x:v>77% is the published 2050 secondary-production result; 65% and 85% are analyst-selected sensitivity brackets. Applying it to these market recipes is a modelling choice; full recovery burdens are retained.</x:v>
       </x:c>
       <x:c r="C32" s="31"/>
       <x:c r="D32" s="31"/>
@@ -6033,12 +6102,12 @@
         <x:v>van_der_voet_2019</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="100" customHeight="1">
+    <x:row r="33" ht="116" customHeight="1">
       <x:c r="A33" s="31" t="str">
         <x:v>lithium carbonate, battery grade</x:v>
       </x:c>
       <x:c r="B33" s="31" t="str">
-        <x:v>Interpolate the minimum linearly between the documented 2020 reference fraction and the 2050 endpoint, with endpoint clamping, as requested by the user. This interpolation is a modelling assumption, not an IEA intermediate-year recycling forecast. Conservative and moderate use the same STEPS-context endpoint; high uses HDS. A higher native share is retained. The global elemental-Li fraction is applied to this carbonate market as a representative-compound sensitivity, not a verified battery-grade forecast. Reference and primary-only remain explicit counterfactuals; native baseline is unchanged.</x:v>
+        <x:v>Conservative 15% is an analyst lower-collection floor. Moderate/high use independently rechecked approximate 250/1122 and 560/1501 global elemental-Li ratios, not battery-grade carbonate forecasts. Linear 2020-2050 interpolation and generic recovered-carbonate grade equivalence are declared sensitivities. Higher native shares are retained. Battery-grade GLO remains native.</x:v>
       </x:c>
       <x:c r="C33" s="31"/>
       <x:c r="D33" s="31"/>
@@ -6108,12 +6177,12 @@
         <x:v>jm_pgm_2026</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="128" customHeight="1">
+    <x:row r="38" ht="116" customHeight="1">
       <x:c r="A38" s="31" t="str">
         <x:v>lithium carbonate</x:v>
       </x:c>
       <x:c r="B38" s="31" t="str">
-        <x:v>GLO same-product hydrometallurgical recovery already supplies 0.08404146%. Rescale existing supplies, retaining recovery burdens, primary weights and logistics. IEA 2026 elemental-Li endpoints250/1122 and560/1501 are representative-compound sensitivities. Ordinary hydroxide benefits via its existing carbonate input (observed1.622797 kg/kg), without another floor or credit. Battery-grade GLO remains native. RELICS Lithium-only factors omit Spodumene; the indicator is not complete elemental-Li extraction.</x:v>
+        <x:v>Conservative 15% is analyst-selected; moderate/high use approximate 250/1122 and 560/1501 global elemental-Li ratios. Rescale only existing GLO same-product recovery, retaining burdens, primary weights and logistics. Ordinary hydroxide benefits via its carbonate input, with no extra credit. Grade transfer remains a sensitivity; RELICS omits Spodumene.</x:v>
       </x:c>
       <x:c r="C38" s="31"/>
       <x:c r="D38" s="31"/>
@@ -6122,6 +6191,81 @@
       <x:c r="G38" s="31" t="str">
         <x:v>iea_critical_minerals_2026, iea_recycling_2024; exported GLO inventory audit, 22 October 2026</x:v>
       </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="18" t="str">
+        <x:v>Candidate scope</x:v>
+      </x:c>
+      <x:c r="B40" s="18" t="str">
+        <x:v>Evidence family / source</x:v>
+      </x:c>
+      <x:c r="C40" s="18"/>
+      <x:c r="D40" s="18"/>
+      <x:c r="E40" s="18" t="str">
+        <x:v>Applicability; no new market rule is enabled</x:v>
+      </x:c>
+      <x:c r="F40" s="18"/>
+      <x:c r="G40" s="18"/>
+    </x:row>
+    <x:row r="41" ht="154" customHeight="1">
+      <x:c r="A41" s="31" t="str">
+        <x:v>rare_earths</x:v>
+      </x:c>
+      <x:c r="B41" s="31" t="str">
+        <x:v>https://www.iea.org/reports/global-critical-minerals-outlook-2025/overview-of-outlook-for-key-minerals | https://iea.blob.core.windows.net/assets/a33abe2e-f799-4787-b09b-2484a6f5a8e4/GlobalCriticalMineralsOutlook2025.pdf</x:v>
+      </x:c>
+      <x:c r="C41" s="31"/>
+      <x:c r="D41" s="31"/>
+      <x:c r="E41" s="31" t="str">
+        <x:v>20/30/39% apply only to magnet Nd/Pr/Dy/Tb supply/reuse proxies. IEA 2025 p177 gives &gt;30/35/39%; 20/30 are deliberately lower sensitivities. Thirteen non-magnet REE products hold reference curves via evidence_scope=reference_only. All REE markets remain native until equivalent recovery LCIs pass review.</x:v>
+      </x:c>
+      <x:c r="F41" s="31"/>
+      <x:c r="G41" s="31"/>
+    </x:row>
+    <x:row r="42" ht="154" customHeight="1">
+      <x:c r="A42" s="31" t="str">
+        <x:v>graphite</x:v>
+      </x:c>
+      <x:c r="B42" s="31" t="str">
+        <x:v>https://www.iea.org/reports/graphite-2 | https://www.iea.org/reports/graphite | https://www.iea.org/data-and-statistics/charts/secondary-supply-volumes-and-share-of-total-demand-for-graphite-in-the-announced-pledges-scenario-and-net-zero-emissions-by-2050-scenario-2023-2050</x:v>
+      </x:c>
+      <x:c r="C42" s="31"/>
+      <x:c r="D42" s="31"/>
+      <x:c r="E42" s="31" t="str">
+        <x:v>3/10/20% are analyst 2050 sensitivities, not a verified common trajectory. IEA 2025 STEPS 2040 secondary supply + reuse is about 2.1%; IEA 2024 APS 2040 is about 15.5%, with different scenarios. No compatible recycled-grade route is approved, so graphite stays native.</x:v>
+      </x:c>
+      <x:c r="F42" s="31"/>
+      <x:c r="G42" s="31"/>
+    </x:row>
+    <x:row r="43" ht="154" customHeight="1">
+      <x:c r="A43" s="31" t="str">
+        <x:v>nonmetal_low</x:v>
+      </x:c>
+      <x:c r="B43" s="31" t="str">
+        <x:v>Family-level heuristic; no direct forecast source</x:v>
+      </x:c>
+      <x:c r="C43" s="31"/>
+      <x:c r="D43" s="31"/>
+      <x:c r="E43" s="31" t="str">
+        <x:v>Zero is a structural choice for explicit primary-only flows, not a global statement that non-metals cannot be recycled. Existing unsupported mineral markets are not overridden. Glass, aggregates and other secondary-capable materials require their own evidence and compatible inventories.</x:v>
+      </x:c>
+      <x:c r="F43" s="31"/>
+      <x:c r="G43" s="31"/>
+    </x:row>
+    <x:row r="44" ht="154" customHeight="1">
+      <x:c r="A44" s="31" t="str">
+        <x:v>base_low</x:v>
+      </x:c>
+      <x:c r="B44" s="31" t="str">
+        <x:v>https://www.oecd.org/content/dam/oecd/en/publications/support-materials/2019/02/global-material-resources-outlook-to-2060_g1g98d7d/highlights-global-material-resources-outlook-to-2060.pdf | https://www.iea.org/reports/the-role-of-critical-minerals-in-clean-energy-transitions/the-state-of-play</x:v>
+      </x:c>
+      <x:c r="C44" s="31"/>
+      <x:c r="D44" s="31"/>
+      <x:c r="E44" s="31" t="str">
+        <x:v>base_low / precious_metals / pgm are heuristic candidate families only. Generic percentages are not forecasts or permission to expand recycling. Retain native markets until evidence, grade, collection boundary and a burden-bearing recovery recipe are qualified.</x:v>
+      </x:c>
+      <x:c r="F44" s="31"/>
+      <x:c r="G44" s="31"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -6163,6 +6307,14 @@
     <x:mergeCell ref="B36:F36"/>
     <x:mergeCell ref="B37:F37"/>
     <x:mergeCell ref="B38:F38"/>
+    <x:mergeCell ref="B41:D41"/>
+    <x:mergeCell ref="E41:G41"/>
+    <x:mergeCell ref="B42:D42"/>
+    <x:mergeCell ref="E42:G42"/>
+    <x:mergeCell ref="B43:D43"/>
+    <x:mergeCell ref="E43:G43"/>
+    <x:mergeCell ref="B44:D44"/>
+    <x:mergeCell ref="E44:G44"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
